--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Aircraft_Cumulative_Statistics_2019.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Aircraft_Cumulative_Statistics_2019.xlsx
@@ -13,75 +13,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="48">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-500</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A220-100</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B737-9</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A330-900</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -163,10 +202,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -186,40 +225,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -227,40 +266,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>50415205582</v>
+        <v>4152009552</v>
       </c>
       <c r="C2" s="0">
-        <v>59713777009</v>
+        <v>5149508147</v>
       </c>
       <c r="D2" s="0">
-        <v>695965</v>
+        <v>84142</v>
       </c>
       <c r="E2" s="0">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>276544</v>
+        <v>298913</v>
       </c>
       <c r="G2" s="0">
-        <v>3.2200000000000002</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>10.75</v>
+        <v>7.29</v>
       </c>
       <c r="I2" s="0">
-        <v>84.430000000000007</v>
+        <v>80.629999999999995</v>
       </c>
       <c r="J2" s="0">
-        <v>1317</v>
+        <v>345</v>
       </c>
       <c r="K2" s="0">
-        <v>3864</v>
+        <v>516.5</v>
       </c>
       <c r="L2" s="0">
-        <v>23.670000000000002</v>
+        <v>10.33</v>
       </c>
       <c r="M2" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.044999999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -268,40 +307,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>13339526082</v>
+        <v>7084744886</v>
       </c>
       <c r="C3" s="0">
-        <v>15863112543</v>
+        <v>8915925051</v>
       </c>
       <c r="D3" s="0">
-        <v>507782</v>
+        <v>96828</v>
       </c>
       <c r="E3" s="0">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>106258</v>
+        <v>491979</v>
       </c>
       <c r="G3" s="0">
-        <v>3.3999999999999999</v>
+        <v>5.3399999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>7.75</v>
+        <v>7.7699999999999996</v>
       </c>
       <c r="I3" s="0">
-        <v>84.090000000000003</v>
+        <v>79.459999999999994</v>
       </c>
       <c r="J3" s="0">
-        <v>871</v>
+        <v>362</v>
       </c>
       <c r="K3" s="0">
-        <v>3793</v>
+        <v>1504</v>
       </c>
       <c r="L3" s="0">
-        <v>22.140000000000001</v>
+        <v>30.079999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="4">
@@ -309,40 +348,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>210838822730</v>
+        <v>3281730300</v>
       </c>
       <c r="C4" s="0">
-        <v>246409171517</v>
+        <v>4177037267</v>
       </c>
       <c r="D4" s="0">
-        <v>812910</v>
+        <v>191783</v>
       </c>
       <c r="E4" s="0">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0">
-        <v>1086789</v>
+        <v>100474</v>
       </c>
       <c r="G4" s="0">
-        <v>3.5899999999999999</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="H4" s="0">
-        <v>11.19</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>85.560000000000002</v>
+        <v>78.569999999999993</v>
       </c>
       <c r="J4" s="0">
-        <v>1218</v>
+        <v>596</v>
       </c>
       <c r="K4" s="0">
-        <v>5605</v>
+        <v>1406.8399999999999</v>
       </c>
       <c r="L4" s="0">
-        <v>31.039999999999999</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="5">
@@ -350,40 +389,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>205070083536</v>
+        <v>28646500192</v>
       </c>
       <c r="C5" s="0">
-        <v>235945861860</v>
+        <v>35802849695</v>
       </c>
       <c r="D5" s="0">
-        <v>825967</v>
+        <v>189573</v>
       </c>
       <c r="E5" s="0">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="F5" s="0">
-        <v>960597</v>
+        <v>730599</v>
       </c>
       <c r="G5" s="0">
-        <v>3.3599999999999999</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>10.68</v>
+        <v>7.9800000000000004</v>
       </c>
       <c r="I5" s="0">
-        <v>86.909999999999997</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="J5" s="0">
-        <v>1277</v>
+        <v>648</v>
       </c>
       <c r="K5" s="0">
-        <v>4838</v>
+        <v>1297.4100000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>25.98</v>
+        <v>17.16</v>
       </c>
       <c r="M5" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +430,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>24191529199</v>
+        <v>66359511</v>
       </c>
       <c r="C6" s="0">
-        <v>28103915678</v>
+        <v>83292450</v>
       </c>
       <c r="D6" s="0">
-        <v>833697</v>
+        <v>55528</v>
       </c>
       <c r="E6" s="0">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0">
-        <v>138561</v>
+        <v>4609</v>
       </c>
       <c r="G6" s="0">
-        <v>4.1100000000000003</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>11.550000000000001</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="I6" s="0">
-        <v>86.079999999999998</v>
+        <v>79.670000000000002</v>
       </c>
       <c r="J6" s="0">
-        <v>1050</v>
+        <v>361</v>
       </c>
       <c r="K6" s="0">
-        <v>3896</v>
+        <v>1270.29</v>
       </c>
       <c r="L6" s="0">
-        <v>20.190000000000001</v>
+        <v>25.41</v>
       </c>
       <c r="M6" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +471,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>17809813684</v>
+        <v>10043560726</v>
       </c>
       <c r="C7" s="0">
-        <v>20564411683</v>
+        <v>12609704137</v>
       </c>
       <c r="D7" s="0">
-        <v>976932</v>
+        <v>155675</v>
       </c>
       <c r="E7" s="0">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="F7" s="0">
-        <v>89355</v>
+        <v>401212</v>
       </c>
       <c r="G7" s="0">
-        <v>4.2400000000000002</v>
+        <v>4.9500000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>10.16</v>
+        <v>8.2599999999999998</v>
       </c>
       <c r="I7" s="0">
-        <v>86.609999999999999</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="J7" s="0">
-        <v>961</v>
+        <v>462</v>
       </c>
       <c r="K7" s="0">
-        <v>6181</v>
+        <v>1290.8900000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>27.550000000000001</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="M7" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +512,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>53617847335</v>
+        <v>6235219049</v>
       </c>
       <c r="C8" s="0">
-        <v>63829153132</v>
+        <v>7732527333</v>
       </c>
       <c r="D8" s="0">
-        <v>689523</v>
+        <v>274690</v>
       </c>
       <c r="E8" s="0">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="F8" s="0">
-        <v>369234</v>
+        <v>149363</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9900000000000002</v>
+        <v>5.3099999999999996</v>
       </c>
       <c r="H8" s="0">
-        <v>11.85</v>
+        <v>9.4299999999999997</v>
       </c>
       <c r="I8" s="0">
-        <v>84</v>
+        <v>80.640000000000001</v>
       </c>
       <c r="J8" s="0">
-        <v>1137</v>
+        <v>519</v>
       </c>
       <c r="K8" s="0">
-        <v>3910</v>
+        <v>3551</v>
       </c>
       <c r="L8" s="0">
-        <v>26.16</v>
+        <v>35.579999999999998</v>
       </c>
       <c r="M8" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +553,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>131375009633</v>
+        <v>16001537037</v>
       </c>
       <c r="C9" s="0">
-        <v>157288255663</v>
+        <v>19890971885</v>
       </c>
       <c r="D9" s="0">
-        <v>573354</v>
+        <v>205634</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="F9" s="0">
-        <v>1367938</v>
+        <v>523996</v>
       </c>
       <c r="G9" s="0">
-        <v>4.9900000000000002</v>
+        <v>5.4199999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>10.140000000000001</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="I9" s="0">
-        <v>83.519999999999996</v>
+        <v>80.450000000000003</v>
       </c>
       <c r="J9" s="0">
-        <v>748</v>
+        <v>499</v>
       </c>
       <c r="K9" s="0">
-        <v>3846</v>
+        <v>1138.7</v>
       </c>
       <c r="L9" s="0">
-        <v>25.149999999999999</v>
+        <v>14.960000000000001</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +594,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>35245109332</v>
+        <v>1768271368</v>
       </c>
       <c r="C10" s="0">
-        <v>41817093806</v>
+        <v>2099179520</v>
       </c>
       <c r="D10" s="0">
-        <v>850460</v>
+        <v>338032</v>
       </c>
       <c r="E10" s="0">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="F10" s="0">
-        <v>225262</v>
+        <v>20023</v>
       </c>
       <c r="G10" s="0">
-        <v>4.5800000000000001</v>
+        <v>3.2200000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>12.24</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="I10" s="0">
-        <v>84.280000000000001</v>
+        <v>84.239999999999995</v>
       </c>
       <c r="J10" s="0">
-        <v>1009</v>
+        <v>962</v>
       </c>
       <c r="K10" s="0">
-        <v>3475</v>
+        <v>3523.9099999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>18.879999999999999</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +635,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>5267390979</v>
+        <v>50295438770</v>
       </c>
       <c r="C11" s="0">
-        <v>6638788455</v>
+        <v>59319937722</v>
       </c>
       <c r="D11" s="0">
-        <v>610744</v>
+        <v>489479</v>
       </c>
       <c r="E11" s="0">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="F11" s="0">
-        <v>30320</v>
+        <v>508792</v>
       </c>
       <c r="G11" s="0">
-        <v>2.79</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="H11" s="0">
-        <v>8.6699999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="I11" s="0">
-        <v>79.340000000000003</v>
+        <v>84.790000000000006</v>
       </c>
       <c r="J11" s="0">
-        <v>1223</v>
+        <v>868</v>
       </c>
       <c r="K11" s="0">
-        <v>3765</v>
+        <v>3504.0799999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>21.050000000000001</v>
+        <v>26.149999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +676,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>213040596842</v>
+        <v>97547997188</v>
       </c>
       <c r="C12" s="0">
-        <v>252985679341</v>
+        <v>115846730618</v>
       </c>
       <c r="D12" s="0">
-        <v>65535</v>
+        <v>650349</v>
       </c>
       <c r="E12" s="0">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F12" s="0">
-        <v>795961</v>
+        <v>714600</v>
       </c>
       <c r="G12" s="0">
-        <v>65535</v>
+        <v>4.0099999999999998</v>
       </c>
       <c r="H12" s="0">
-        <v>65535</v>
+        <v>10.82</v>
       </c>
       <c r="I12" s="0">
-        <v>84.209999999999994</v>
+        <v>84.200000000000003</v>
       </c>
       <c r="J12" s="0">
-        <v>1599</v>
+        <v>1012</v>
       </c>
       <c r="K12" s="0">
-        <v>5375</v>
+        <v>4156.4899999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>27.870000000000001</v>
+        <v>25.969999999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="13">
@@ -678,40 +717,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>924456688</v>
+        <v>13854235199</v>
       </c>
       <c r="C13" s="0">
-        <v>1115505600</v>
+        <v>16210513742</v>
       </c>
       <c r="D13" s="0">
-        <v>65535</v>
+        <v>796977</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="F13" s="0">
-        <v>57913</v>
+        <v>83764</v>
       </c>
       <c r="G13" s="0">
-        <v>65535</v>
+        <v>4.1200000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>65535</v>
+        <v>11.49</v>
       </c>
       <c r="I13" s="0">
-        <v>82.870000000000005</v>
+        <v>85.459999999999994</v>
       </c>
       <c r="J13" s="0">
-        <v>385</v>
+        <v>1045</v>
       </c>
       <c r="K13" s="0">
-        <v>0</v>
+        <v>3733.4699999999998</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="M13" s="0">
-        <v>0</v>
+        <v>0.053999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +758,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>7332664097</v>
+        <v>111293552706</v>
       </c>
       <c r="C14" s="0">
-        <v>9072388648</v>
+        <v>127141389815</v>
       </c>
       <c r="D14" s="0">
-        <v>160346</v>
+        <v>816842</v>
       </c>
       <c r="E14" s="0">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="F14" s="0">
-        <v>272740</v>
+        <v>538431</v>
       </c>
       <c r="G14" s="0">
-        <v>4.8200000000000003</v>
+        <v>3.46</v>
       </c>
       <c r="H14" s="0">
-        <v>8.1899999999999995</v>
+        <v>11.220000000000001</v>
       </c>
       <c r="I14" s="0">
-        <v>80.819999999999993</v>
+        <v>87.540000000000006</v>
       </c>
       <c r="J14" s="0">
-        <v>469</v>
+        <v>1271</v>
       </c>
       <c r="K14" s="0">
-        <v>1163</v>
+        <v>4593.5799999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>16.629999999999999</v>
+        <v>24.620000000000001</v>
       </c>
       <c r="M14" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +799,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>6237554885</v>
+        <v>6650934318</v>
       </c>
       <c r="C15" s="0">
-        <v>7900825477</v>
+        <v>7749661212</v>
       </c>
       <c r="D15" s="0">
-        <v>55020</v>
+        <v>707086</v>
       </c>
       <c r="E15" s="0">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="F15" s="0">
-        <v>237676</v>
+        <v>19418</v>
       </c>
       <c r="G15" s="0">
-        <v>1.6599999999999999</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="0">
-        <v>2.9199999999999999</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="I15" s="0">
-        <v>78.950000000000003</v>
+        <v>85.819999999999993</v>
       </c>
       <c r="J15" s="0">
-        <v>507</v>
+        <v>2105</v>
       </c>
       <c r="K15" s="0">
-        <v>1292</v>
+        <v>4791.8000000000002</v>
       </c>
       <c r="L15" s="0">
-        <v>20.109999999999999</v>
+        <v>25.27</v>
       </c>
       <c r="M15" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +840,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>2361457510</v>
+        <v>9007248942</v>
       </c>
       <c r="C16" s="0">
-        <v>2894390204</v>
+        <v>10781165880</v>
       </c>
       <c r="D16" s="0">
-        <v>146181</v>
+        <v>269125</v>
       </c>
       <c r="E16" s="0">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F16" s="0">
-        <v>82369</v>
+        <v>219893</v>
       </c>
       <c r="G16" s="0">
-        <v>4.1600000000000001</v>
+        <v>5.4900000000000002</v>
       </c>
       <c r="H16" s="0">
-        <v>7.2400000000000002</v>
+        <v>8.1600000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>81.590000000000003</v>
+        <v>83.549999999999997</v>
       </c>
       <c r="J16" s="0">
-        <v>501</v>
+        <v>439</v>
       </c>
       <c r="K16" s="0">
-        <v>1222</v>
+        <v>3870.3600000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>17.449999999999999</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="M16" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.11700000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +881,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>2046791540</v>
+        <v>89642339332</v>
       </c>
       <c r="C17" s="0">
-        <v>2492594724</v>
+        <v>108026106191</v>
       </c>
       <c r="D17" s="0">
-        <v>245576</v>
+        <v>511560</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F17" s="0">
-        <v>51325</v>
+        <v>1118690</v>
       </c>
       <c r="G17" s="0">
-        <v>5.0599999999999996</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>9.9399999999999995</v>
+        <v>10.140000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>82.109999999999999</v>
+        <v>82.980000000000004</v>
       </c>
       <c r="J17" s="0">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="K17" s="0">
-        <v>711</v>
+        <v>3987.8099999999999</v>
       </c>
       <c r="L17" s="0">
-        <v>9.3499999999999996</v>
+        <v>28.239999999999998</v>
       </c>
       <c r="M17" s="0">
-        <v>0.029999999999999999</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +922,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>8861995601</v>
+        <v>165442954314</v>
       </c>
       <c r="C18" s="0">
-        <v>10905561178</v>
+        <v>195524972924</v>
       </c>
       <c r="D18" s="0">
-        <v>235034</v>
+        <v>672508</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="F18" s="0">
-        <v>248076</v>
+        <v>1086401</v>
       </c>
       <c r="G18" s="0">
-        <v>5.3499999999999996</v>
+        <v>3.7400000000000002</v>
       </c>
       <c r="H18" s="0">
-        <v>9.8399999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="I18" s="0">
-        <v>81.260000000000005</v>
+        <v>84.609999999999999</v>
       </c>
       <c r="J18" s="0">
-        <v>578</v>
+        <v>1079</v>
       </c>
       <c r="K18" s="0">
-        <v>966</v>
+        <v>4106.1400000000003</v>
       </c>
       <c r="L18" s="0">
-        <v>12.710000000000001</v>
+        <v>24.640000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +963,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>1420097670</v>
+        <v>2201106780</v>
       </c>
       <c r="C19" s="0">
-        <v>1753881100</v>
+        <v>2737201777</v>
       </c>
       <c r="D19" s="0">
-        <v>65535</v>
+        <v>198780</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="F19" s="0">
-        <v>125604</v>
+        <v>14761</v>
       </c>
       <c r="G19" s="0">
-        <v>65535</v>
+        <v>1.0700000000000001</v>
       </c>
       <c r="H19" s="0">
-        <v>65535</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="I19" s="0">
-        <v>80.969999999999999</v>
+        <v>80.409999999999997</v>
       </c>
       <c r="J19" s="0">
-        <v>279</v>
+        <v>1067</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>5872.8500000000004</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +1004,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>6081711424</v>
+        <v>4726136143</v>
       </c>
       <c r="C20" s="0">
-        <v>7713542482</v>
+        <v>5538368724</v>
       </c>
       <c r="D20" s="0">
-        <v>151157</v>
+        <v>632956</v>
       </c>
       <c r="E20" s="0">
-        <v>67</v>
+        <v>178</v>
       </c>
       <c r="F20" s="0">
-        <v>288027</v>
+        <v>31851</v>
       </c>
       <c r="G20" s="0">
-        <v>5.6399999999999997</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>8.8000000000000007</v>
+        <v>9.5800000000000001</v>
       </c>
       <c r="I20" s="0">
-        <v>78.840000000000003</v>
+        <v>85.329999999999998</v>
       </c>
       <c r="J20" s="0">
-        <v>399</v>
+        <v>974</v>
       </c>
       <c r="K20" s="0">
-        <v>1429</v>
+        <v>6007.6300000000001</v>
       </c>
       <c r="L20" s="0">
-        <v>21.32</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="M20" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1045,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>11382190579</v>
+        <v>88665958114</v>
       </c>
       <c r="C21" s="0">
-        <v>14758502737</v>
+        <v>101712517504</v>
       </c>
       <c r="D21" s="0">
-        <v>211834</v>
+        <v>824652</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="F21" s="0">
-        <v>336899</v>
+        <v>442271</v>
       </c>
       <c r="G21" s="0">
-        <v>4.8399999999999999</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="H21" s="0">
-        <v>9.6799999999999997</v>
+        <v>11.6</v>
       </c>
       <c r="I21" s="0">
-        <v>77.120000000000005</v>
+        <v>87.170000000000002</v>
       </c>
       <c r="J21" s="0">
-        <v>591</v>
+        <v>1284</v>
       </c>
       <c r="K21" s="0">
-        <v>1420</v>
+        <v>3803.0500000000002</v>
       </c>
       <c r="L21" s="0">
-        <v>19.170000000000002</v>
+        <v>21.23</v>
       </c>
       <c r="M21" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.052999999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1086,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>22627522210</v>
+        <v>533418168</v>
       </c>
       <c r="C22" s="0">
-        <v>28022096482</v>
+        <v>664032004</v>
       </c>
       <c r="D22" s="0">
-        <v>192037</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="F22" s="0">
-        <v>851153</v>
+        <v>2484</v>
       </c>
       <c r="G22" s="0">
-        <v>5.8300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0">
-        <v>10.15</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>80.75</v>
+        <v>80.329999999999998</v>
       </c>
       <c r="J22" s="0">
-        <v>500</v>
+        <v>1493</v>
       </c>
       <c r="K22" s="0">
-        <v>1409</v>
+        <v>4964.8400000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>21.77</v>
+        <v>27.739999999999998</v>
       </c>
       <c r="M22" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="23">
@@ -1088,40 +1127,573 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
+        <v>47935061897</v>
+      </c>
+      <c r="C23" s="0">
+        <v>54231008623</v>
+      </c>
+      <c r="D23" s="0">
+        <v>820936</v>
+      </c>
+      <c r="E23" s="0">
+        <v>182</v>
+      </c>
+      <c r="F23" s="0">
+        <v>184259</v>
+      </c>
+      <c r="G23" s="0">
+        <v>2.79</v>
+      </c>
+      <c r="H23" s="0">
+        <v>10.98</v>
+      </c>
+      <c r="I23" s="0">
+        <v>88.390000000000001</v>
+      </c>
+      <c r="J23" s="0">
+        <v>1645</v>
+      </c>
+      <c r="K23" s="0">
+        <v>4931.1099999999997</v>
+      </c>
+      <c r="L23" s="0">
+        <v>27.489999999999998</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>11893993789</v>
+      </c>
+      <c r="C24" s="0">
+        <v>13508447609</v>
+      </c>
+      <c r="D24" s="0">
+        <v>1006591</v>
+      </c>
+      <c r="E24" s="0">
+        <v>234</v>
+      </c>
+      <c r="F24" s="0">
+        <v>35352</v>
+      </c>
+      <c r="G24" s="0">
+        <v>2.6299999999999999</v>
+      </c>
+      <c r="H24" s="0">
+        <v>10.24</v>
+      </c>
+      <c r="I24" s="0">
+        <v>88.049999999999997</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1633</v>
+      </c>
+      <c r="K24" s="0">
+        <v>5409.0799999999999</v>
+      </c>
+      <c r="L24" s="0">
+        <v>23.120000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>38983770971</v>
+      </c>
+      <c r="C25" s="0">
+        <v>46295620313</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>213</v>
+      </c>
+      <c r="F25" s="0">
+        <v>62231</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0</v>
+      </c>
+      <c r="I25" s="0">
+        <v>84.209999999999994</v>
+      </c>
+      <c r="J25" s="0">
+        <v>3486</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6796.1999999999998</v>
+      </c>
+      <c r="L25" s="0">
+        <v>31.859999999999999</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.068000000000000005</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>15381428931</v>
+      </c>
+      <c r="C26" s="0">
+        <v>17997226658</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
+        <v>242</v>
+      </c>
+      <c r="F26" s="0">
+        <v>20000</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0">
+        <v>85.469999999999999</v>
+      </c>
+      <c r="J26" s="0">
+        <v>3725</v>
+      </c>
+      <c r="K26" s="0">
+        <v>6753.1899999999996</v>
+      </c>
+      <c r="L26" s="0">
+        <v>27.960000000000001</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.058999999999999997</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>23791003183</v>
+      </c>
+      <c r="C27" s="0">
+        <v>28219020422</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1623649</v>
+      </c>
+      <c r="E27" s="0">
+        <v>260</v>
+      </c>
+      <c r="F27" s="0">
+        <v>31722</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.8300000000000001</v>
+      </c>
+      <c r="H27" s="0">
+        <v>13.41</v>
+      </c>
+      <c r="I27" s="0">
+        <v>84.310000000000002</v>
+      </c>
+      <c r="J27" s="0">
+        <v>3445</v>
+      </c>
+      <c r="K27" s="0">
+        <v>7730.7700000000004</v>
+      </c>
+      <c r="L27" s="0">
+        <v>29.920000000000002</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>22893534970</v>
+      </c>
+      <c r="C28" s="0">
+        <v>26889504124</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1938681</v>
+      </c>
+      <c r="E28" s="0">
+        <v>291</v>
+      </c>
+      <c r="F28" s="0">
+        <v>22537</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1.6200000000000001</v>
+      </c>
+      <c r="H28" s="0">
+        <v>13.869999999999999</v>
+      </c>
+      <c r="I28" s="0">
+        <v>85.140000000000001</v>
+      </c>
+      <c r="J28" s="0">
+        <v>4096</v>
+      </c>
+      <c r="K28" s="0">
+        <v>7631.8599999999997</v>
+      </c>
+      <c r="L28" s="0">
+        <v>26.199999999999999</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>847679219</v>
+      </c>
+      <c r="C29" s="0">
+        <v>1013162706</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1608195</v>
+      </c>
+      <c r="E29" s="0">
+        <v>280</v>
+      </c>
+      <c r="F29" s="0">
+        <v>680</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.0800000000000001</v>
+      </c>
+      <c r="H29" s="0">
+        <v>11.789999999999999</v>
+      </c>
+      <c r="I29" s="0">
+        <v>83.670000000000002</v>
+      </c>
+      <c r="J29" s="0">
+        <v>5315</v>
+      </c>
+      <c r="K29" s="0">
+        <v>6881.9399999999996</v>
+      </c>
+      <c r="L29" s="0">
+        <v>24.550000000000001</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>9566236554</v>
+      </c>
+      <c r="C30" s="0">
+        <v>11200460405</v>
+      </c>
+      <c r="D30" s="0">
+        <v>2408701</v>
+      </c>
+      <c r="E30" s="0">
+        <v>305</v>
+      </c>
+      <c r="F30" s="0">
+        <v>5980</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.29</v>
+      </c>
+      <c r="H30" s="0">
+        <v>15.470000000000001</v>
+      </c>
+      <c r="I30" s="0">
+        <v>85.409999999999997</v>
+      </c>
+      <c r="J30" s="0">
+        <v>6139</v>
+      </c>
+      <c r="K30" s="0">
+        <v>7491.8299999999999</v>
+      </c>
+      <c r="L30" s="0">
+        <v>24.559999999999999</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.048000000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>13046758010</v>
+      </c>
+      <c r="C31" s="0">
+        <v>15577601393</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1492107</v>
+      </c>
+      <c r="E31" s="0">
+        <v>228</v>
+      </c>
+      <c r="F31" s="0">
+        <v>17686</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.6899999999999999</v>
+      </c>
+      <c r="H31" s="0">
+        <v>13.380000000000001</v>
+      </c>
+      <c r="I31" s="0">
+        <v>83.75</v>
+      </c>
+      <c r="J31" s="0">
+        <v>3883</v>
+      </c>
+      <c r="K31" s="0">
+        <v>8280.1499999999996</v>
+      </c>
+      <c r="L31" s="0">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.073999999999999996</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>27220559776</v>
+      </c>
+      <c r="C32" s="0">
+        <v>32692611730</v>
+      </c>
+      <c r="D32" s="0">
+        <v>2094338</v>
+      </c>
+      <c r="E32" s="0">
+        <v>267</v>
+      </c>
+      <c r="F32" s="0">
+        <v>21800</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H32" s="0">
+        <v>15.460000000000001</v>
+      </c>
+      <c r="I32" s="0">
+        <v>83.260000000000005</v>
+      </c>
+      <c r="J32" s="0">
+        <v>5651</v>
+      </c>
+      <c r="K32" s="0">
+        <v>8692.1399999999994</v>
+      </c>
+      <c r="L32" s="0">
+        <v>32.719999999999999</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>4782436290</v>
+      </c>
+      <c r="C33" s="0">
+        <v>5372651340</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0">
+        <v>318</v>
+      </c>
+      <c r="F33" s="0">
+        <v>4977</v>
+      </c>
+      <c r="G33" s="0">
+        <v>0</v>
+      </c>
+      <c r="H33" s="0">
+        <v>0</v>
+      </c>
+      <c r="I33" s="0">
+        <v>89.010000000000005</v>
+      </c>
+      <c r="J33" s="0">
+        <v>3395</v>
+      </c>
+      <c r="K33" s="0">
+        <v>5578.6599999999999</v>
+      </c>
+      <c r="L33" s="0">
+        <v>17.539999999999999</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.035999999999999997</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>71307801505</v>
+      </c>
+      <c r="C34" s="0">
+        <v>85462342476</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1783066</v>
+      </c>
+      <c r="E34" s="0">
+        <v>293</v>
+      </c>
+      <c r="F34" s="0">
+        <v>72294</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.51</v>
+      </c>
+      <c r="H34" s="0">
+        <v>12.699999999999999</v>
+      </c>
+      <c r="I34" s="0">
+        <v>83.439999999999998</v>
+      </c>
+      <c r="J34" s="0">
+        <v>4141</v>
+      </c>
+      <c r="K34" s="0">
+        <v>9419.4699999999993</v>
+      </c>
+      <c r="L34" s="0">
+        <v>32.920000000000002</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>24695859448</v>
+      </c>
+      <c r="C35" s="0">
+        <v>29615257922</v>
+      </c>
+      <c r="D35" s="0">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0">
+        <v>325</v>
+      </c>
+      <c r="F35" s="0">
+        <v>16559</v>
+      </c>
+      <c r="G35" s="0">
+        <v>0</v>
+      </c>
+      <c r="H35" s="0">
+        <v>0</v>
+      </c>
+      <c r="I35" s="0">
+        <v>83.390000000000001</v>
+      </c>
+      <c r="J35" s="0">
+        <v>5462</v>
+      </c>
+      <c r="K35" s="0">
+        <v>10818.790000000001</v>
+      </c>
+      <c r="L35" s="0">
+        <v>33.07</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
         <v>1029487377138</v>
       </c>
-      <c r="C23" s="0">
+      <c r="C36" s="0">
         <v>1215788509319</v>
       </c>
-      <c r="D23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="E23" s="0">
+      <c r="D36" s="0">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0">
         <v>132</v>
       </c>
-      <c r="F23" s="0">
+      <c r="F36" s="0">
         <v>7998601</v>
       </c>
-      <c r="G23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="H23" s="0">
-        <v>65535</v>
-      </c>
-      <c r="I23" s="0">
+      <c r="G36" s="0">
+        <v>0</v>
+      </c>
+      <c r="H36" s="0">
+        <v>0</v>
+      </c>
+      <c r="I36" s="0">
         <v>84.680000000000007</v>
       </c>
-      <c r="J23" s="0">
+      <c r="J36" s="0">
         <v>936</v>
       </c>
-      <c r="K23" s="0">
-        <v>3960</v>
-      </c>
-      <c r="L23" s="0">
+      <c r="K36" s="0">
+        <v>3960.2600000000002</v>
+      </c>
+      <c r="L36" s="0">
         <v>25.91</v>
       </c>
-      <c r="M23" s="0">
-        <v>0.070000000000000007</v>
+      <c r="M36" s="0">
+        <v>0.066000000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Aircraft_Cumulative_Statistics_2019.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Aircraft_Cumulative_Statistics_2019.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53" uniqueCount="53">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,7 +33,10 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -60,7 +66,16 @@
     <t>A321NEO</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -202,7 +217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -225,40 +240,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -266,40 +281,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>4152009552</v>
+        <v>1289199017</v>
       </c>
       <c r="C2" s="0">
-        <v>5149508147</v>
+        <v>1680885599</v>
       </c>
       <c r="D2" s="0">
-        <v>84142</v>
+        <v>30927</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>298913</v>
+        <v>104370</v>
       </c>
       <c r="G2" s="0">
-        <v>4.8799999999999999</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>7.29</v>
+        <v>2.9100000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>80.629999999999995</v>
+        <v>76.700000000000003</v>
       </c>
       <c r="J2" s="0">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="K2" s="0">
-        <v>516.5</v>
+        <v>1292.3699999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>10.33</v>
+        <v>29.370000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.044999999999999998</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="3">
@@ -307,40 +322,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>7084744886</v>
+        <v>4152009552</v>
       </c>
       <c r="C3" s="0">
-        <v>8915925051</v>
+        <v>5149508147</v>
       </c>
       <c r="D3" s="0">
-        <v>96828</v>
+        <v>84142</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>491979</v>
+        <v>298913</v>
       </c>
       <c r="G3" s="0">
-        <v>5.3399999999999999</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>7.7699999999999996</v>
+        <v>7.29</v>
       </c>
       <c r="I3" s="0">
-        <v>79.459999999999994</v>
+        <v>80.629999999999995</v>
       </c>
       <c r="J3" s="0">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="K3" s="0">
-        <v>1504</v>
+        <v>516.5</v>
       </c>
       <c r="L3" s="0">
-        <v>30.079999999999998</v>
+        <v>10.33</v>
       </c>
       <c r="M3" s="0">
-        <v>0.121</v>
+        <v>0.044999999999999998</v>
       </c>
     </row>
     <row r="4">
@@ -348,40 +363,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>3281730300</v>
+        <v>7084744886</v>
       </c>
       <c r="C4" s="0">
-        <v>4177037267</v>
+        <v>8915925051</v>
       </c>
       <c r="D4" s="0">
-        <v>191783</v>
+        <v>96828</v>
       </c>
       <c r="E4" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>100474</v>
+        <v>491979</v>
       </c>
       <c r="G4" s="0">
-        <v>4.6100000000000003</v>
+        <v>5.3399999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>9.4100000000000001</v>
+        <v>7.7699999999999996</v>
       </c>
       <c r="I4" s="0">
-        <v>78.569999999999993</v>
+        <v>79.459999999999994</v>
       </c>
       <c r="J4" s="0">
-        <v>596</v>
+        <v>362</v>
       </c>
       <c r="K4" s="0">
-        <v>1406.8399999999999</v>
+        <v>1504</v>
       </c>
       <c r="L4" s="0">
-        <v>20.190000000000001</v>
+        <v>30.079999999999998</v>
       </c>
       <c r="M4" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="5">
@@ -389,40 +404,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>28646500192</v>
+        <v>3281730300</v>
       </c>
       <c r="C5" s="0">
-        <v>35802849695</v>
+        <v>4177037267</v>
       </c>
       <c r="D5" s="0">
-        <v>189573</v>
+        <v>191783</v>
       </c>
       <c r="E5" s="0">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F5" s="0">
-        <v>730599</v>
+        <v>100474</v>
       </c>
       <c r="G5" s="0">
-        <v>3.8700000000000001</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="H5" s="0">
-        <v>7.9800000000000004</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>80.010000000000005</v>
+        <v>78.569999999999993</v>
       </c>
       <c r="J5" s="0">
-        <v>648</v>
+        <v>596</v>
       </c>
       <c r="K5" s="0">
-        <v>1297.4100000000001</v>
+        <v>1406.8399999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>17.16</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.055</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="6">
@@ -430,40 +445,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>66359511</v>
+        <v>28646500192</v>
       </c>
       <c r="C6" s="0">
-        <v>83292450</v>
+        <v>35802849695</v>
       </c>
       <c r="D6" s="0">
-        <v>55528</v>
+        <v>189573</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F6" s="0">
-        <v>4609</v>
+        <v>730599</v>
       </c>
       <c r="G6" s="0">
-        <v>3.0699999999999998</v>
+        <v>3.8700000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>4.6900000000000004</v>
+        <v>7.9800000000000004</v>
       </c>
       <c r="I6" s="0">
-        <v>79.670000000000002</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="J6" s="0">
-        <v>361</v>
+        <v>648</v>
       </c>
       <c r="K6" s="0">
-        <v>1270.29</v>
+        <v>1297.4100000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>25.41</v>
+        <v>17.16</v>
       </c>
       <c r="M6" s="0">
-        <v>0.107</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="7">
@@ -471,40 +486,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>10043560726</v>
+        <v>1170303614</v>
       </c>
       <c r="C7" s="0">
-        <v>12609704137</v>
+        <v>1493766700</v>
       </c>
       <c r="D7" s="0">
-        <v>155675</v>
+        <v>118930</v>
       </c>
       <c r="E7" s="0">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F7" s="0">
-        <v>401212</v>
+        <v>79994</v>
       </c>
       <c r="G7" s="0">
-        <v>4.9500000000000002</v>
+        <v>6.3700000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>8.2599999999999998</v>
+        <v>7.4299999999999997</v>
       </c>
       <c r="I7" s="0">
-        <v>79.650000000000006</v>
+        <v>78.349999999999994</v>
       </c>
       <c r="J7" s="0">
-        <v>462</v>
+        <v>246</v>
       </c>
       <c r="K7" s="0">
-        <v>1290.8900000000001</v>
+        <v>1979.3199999999999</v>
       </c>
       <c r="L7" s="0">
-        <v>19.010000000000002</v>
+        <v>26.039999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="8">
@@ -512,40 +527,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>6235219049</v>
+        <v>66359511</v>
       </c>
       <c r="C8" s="0">
-        <v>7732527333</v>
+        <v>83292450</v>
       </c>
       <c r="D8" s="0">
-        <v>274690</v>
+        <v>55528</v>
       </c>
       <c r="E8" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F8" s="0">
-        <v>149363</v>
+        <v>4609</v>
       </c>
       <c r="G8" s="0">
-        <v>5.3099999999999996</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="H8" s="0">
-        <v>9.4299999999999997</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="I8" s="0">
-        <v>80.640000000000001</v>
+        <v>79.670000000000002</v>
       </c>
       <c r="J8" s="0">
-        <v>519</v>
+        <v>361</v>
       </c>
       <c r="K8" s="0">
-        <v>3551</v>
+        <v>1270.29</v>
       </c>
       <c r="L8" s="0">
-        <v>35.579999999999998</v>
+        <v>25.41</v>
       </c>
       <c r="M8" s="0">
-        <v>0.122</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="9">
@@ -553,40 +568,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>16001537037</v>
+        <v>10043560726</v>
       </c>
       <c r="C9" s="0">
-        <v>19890971885</v>
+        <v>12609704137</v>
       </c>
       <c r="D9" s="0">
-        <v>205634</v>
+        <v>155675</v>
       </c>
       <c r="E9" s="0">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F9" s="0">
-        <v>523996</v>
+        <v>401212</v>
       </c>
       <c r="G9" s="0">
-        <v>5.4199999999999999</v>
+        <v>4.9500000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>9.3699999999999992</v>
+        <v>8.2599999999999998</v>
       </c>
       <c r="I9" s="0">
-        <v>80.450000000000003</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="J9" s="0">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="K9" s="0">
-        <v>1138.7</v>
+        <v>1290.8900000000001</v>
       </c>
       <c r="L9" s="0">
-        <v>14.960000000000001</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="M9" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="10">
@@ -594,40 +609,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>1768271368</v>
+        <v>6235219049</v>
       </c>
       <c r="C10" s="0">
-        <v>2099179520</v>
+        <v>7732527333</v>
       </c>
       <c r="D10" s="0">
-        <v>338032</v>
+        <v>274690</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F10" s="0">
-        <v>20023</v>
+        <v>149363</v>
       </c>
       <c r="G10" s="0">
-        <v>3.2200000000000002</v>
+        <v>5.3099999999999996</v>
       </c>
       <c r="H10" s="0">
-        <v>8.7300000000000004</v>
+        <v>9.4299999999999997</v>
       </c>
       <c r="I10" s="0">
-        <v>84.239999999999995</v>
+        <v>80.640000000000001</v>
       </c>
       <c r="J10" s="0">
-        <v>962</v>
+        <v>519</v>
       </c>
       <c r="K10" s="0">
-        <v>3523.9099999999999</v>
+        <v>3551</v>
       </c>
       <c r="L10" s="0">
-        <v>32.340000000000003</v>
+        <v>35.579999999999998</v>
       </c>
       <c r="M10" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="11">
@@ -635,40 +650,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>50295438770</v>
+        <v>16001537037</v>
       </c>
       <c r="C11" s="0">
-        <v>59319937722</v>
+        <v>19890971885</v>
       </c>
       <c r="D11" s="0">
-        <v>489479</v>
+        <v>205634</v>
       </c>
       <c r="E11" s="0">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="F11" s="0">
-        <v>508792</v>
+        <v>523996</v>
       </c>
       <c r="G11" s="0">
-        <v>4.2000000000000002</v>
+        <v>5.4199999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>10.16</v>
+        <v>9.3699999999999992</v>
       </c>
       <c r="I11" s="0">
-        <v>84.790000000000006</v>
+        <v>80.450000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>868</v>
+        <v>499</v>
       </c>
       <c r="K11" s="0">
-        <v>3504.0799999999999</v>
+        <v>1138.7</v>
       </c>
       <c r="L11" s="0">
-        <v>26.149999999999999</v>
+        <v>14.960000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -676,40 +691,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>97547997188</v>
+        <v>1768271368</v>
       </c>
       <c r="C12" s="0">
-        <v>115846730618</v>
+        <v>2099179520</v>
       </c>
       <c r="D12" s="0">
-        <v>650349</v>
+        <v>338032</v>
       </c>
       <c r="E12" s="0">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="F12" s="0">
-        <v>714600</v>
+        <v>20023</v>
       </c>
       <c r="G12" s="0">
-        <v>4.0099999999999998</v>
+        <v>3.2200000000000002</v>
       </c>
       <c r="H12" s="0">
-        <v>10.82</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="I12" s="0">
-        <v>84.200000000000003</v>
+        <v>84.239999999999995</v>
       </c>
       <c r="J12" s="0">
-        <v>1012</v>
+        <v>962</v>
       </c>
       <c r="K12" s="0">
-        <v>4156.4899999999998</v>
+        <v>3523.9099999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>25.969999999999999</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="M12" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -717,40 +732,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>13854235199</v>
+        <v>50295438770</v>
       </c>
       <c r="C13" s="0">
-        <v>16210513742</v>
+        <v>59319937722</v>
       </c>
       <c r="D13" s="0">
-        <v>796977</v>
+        <v>489479</v>
       </c>
       <c r="E13" s="0">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="F13" s="0">
-        <v>83764</v>
+        <v>508792</v>
       </c>
       <c r="G13" s="0">
-        <v>4.1200000000000001</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="H13" s="0">
-        <v>11.49</v>
+        <v>10.16</v>
       </c>
       <c r="I13" s="0">
-        <v>85.459999999999994</v>
+        <v>84.790000000000006</v>
       </c>
       <c r="J13" s="0">
-        <v>1045</v>
+        <v>868</v>
       </c>
       <c r="K13" s="0">
-        <v>3733.4699999999998</v>
+        <v>3504.0799999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>20.170000000000002</v>
+        <v>26.149999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0.053999999999999999</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="14">
@@ -758,40 +773,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>111293552706</v>
+        <v>97547997188</v>
       </c>
       <c r="C14" s="0">
-        <v>127141389815</v>
+        <v>115846730618</v>
       </c>
       <c r="D14" s="0">
-        <v>816842</v>
+        <v>650349</v>
       </c>
       <c r="E14" s="0">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="F14" s="0">
-        <v>538431</v>
+        <v>714600</v>
       </c>
       <c r="G14" s="0">
-        <v>3.46</v>
+        <v>4.0099999999999998</v>
       </c>
       <c r="H14" s="0">
-        <v>11.220000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="I14" s="0">
-        <v>87.540000000000006</v>
+        <v>84.200000000000003</v>
       </c>
       <c r="J14" s="0">
-        <v>1271</v>
+        <v>1012</v>
       </c>
       <c r="K14" s="0">
-        <v>4593.5799999999999</v>
+        <v>4156.4899999999998</v>
       </c>
       <c r="L14" s="0">
-        <v>24.620000000000001</v>
+        <v>25.969999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.063</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="15">
@@ -799,40 +814,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>6650934318</v>
+        <v>13854235199</v>
       </c>
       <c r="C15" s="0">
-        <v>7749661212</v>
+        <v>16210513742</v>
       </c>
       <c r="D15" s="0">
-        <v>707086</v>
+        <v>796977</v>
       </c>
       <c r="E15" s="0">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F15" s="0">
-        <v>19418</v>
+        <v>83764</v>
       </c>
       <c r="G15" s="0">
-        <v>1.77</v>
+        <v>4.1200000000000001</v>
       </c>
       <c r="H15" s="0">
-        <v>8.6199999999999992</v>
+        <v>11.49</v>
       </c>
       <c r="I15" s="0">
-        <v>85.819999999999993</v>
+        <v>85.459999999999994</v>
       </c>
       <c r="J15" s="0">
-        <v>2105</v>
+        <v>1045</v>
       </c>
       <c r="K15" s="0">
-        <v>4791.8000000000002</v>
+        <v>3733.4699999999998</v>
       </c>
       <c r="L15" s="0">
-        <v>25.27</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="M15" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.053999999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -840,40 +855,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>9007248942</v>
+        <v>111293552706</v>
       </c>
       <c r="C16" s="0">
-        <v>10781165880</v>
+        <v>127141389815</v>
       </c>
       <c r="D16" s="0">
-        <v>269125</v>
+        <v>816842</v>
       </c>
       <c r="E16" s="0">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="F16" s="0">
-        <v>219893</v>
+        <v>538431</v>
       </c>
       <c r="G16" s="0">
-        <v>5.4900000000000002</v>
+        <v>3.46</v>
       </c>
       <c r="H16" s="0">
-        <v>8.1600000000000001</v>
+        <v>11.220000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>83.549999999999997</v>
+        <v>87.540000000000006</v>
       </c>
       <c r="J16" s="0">
-        <v>439</v>
+        <v>1271</v>
       </c>
       <c r="K16" s="0">
-        <v>3870.3600000000001</v>
+        <v>4593.5799999999999</v>
       </c>
       <c r="L16" s="0">
-        <v>34.380000000000003</v>
+        <v>24.620000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.11700000000000001</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="17">
@@ -881,40 +896,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>89642339332</v>
+        <v>6650934318</v>
       </c>
       <c r="C17" s="0">
-        <v>108026106191</v>
+        <v>7749661212</v>
       </c>
       <c r="D17" s="0">
-        <v>511560</v>
+        <v>707086</v>
       </c>
       <c r="E17" s="0">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="F17" s="0">
-        <v>1118690</v>
+        <v>19418</v>
       </c>
       <c r="G17" s="0">
-        <v>5.2999999999999998</v>
+        <v>1.77</v>
       </c>
       <c r="H17" s="0">
-        <v>10.140000000000001</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="I17" s="0">
-        <v>82.980000000000004</v>
+        <v>85.819999999999993</v>
       </c>
       <c r="J17" s="0">
-        <v>684</v>
+        <v>2105</v>
       </c>
       <c r="K17" s="0">
-        <v>3987.8099999999999</v>
+        <v>4791.8000000000002</v>
       </c>
       <c r="L17" s="0">
-        <v>28.239999999999998</v>
+        <v>25.27</v>
       </c>
       <c r="M17" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -922,40 +937,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>165442954314</v>
+        <v>9446378986</v>
       </c>
       <c r="C18" s="0">
-        <v>195524972924</v>
+        <v>11126202187</v>
       </c>
       <c r="D18" s="0">
-        <v>672508</v>
+        <v>356495</v>
       </c>
       <c r="E18" s="0">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="F18" s="0">
-        <v>1086401</v>
+        <v>161139</v>
       </c>
       <c r="G18" s="0">
-        <v>3.7400000000000002</v>
+        <v>5.1600000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>10.48</v>
+        <v>8.0999999999999996</v>
       </c>
       <c r="I18" s="0">
-        <v>84.609999999999999</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="J18" s="0">
-        <v>1079</v>
+        <v>470</v>
       </c>
       <c r="K18" s="0">
-        <v>4106.1400000000003</v>
+        <v>4208.2200000000003</v>
       </c>
       <c r="L18" s="0">
-        <v>24.640000000000001</v>
+        <v>28.620000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -963,40 +978,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>2201106780</v>
+        <v>4660595026</v>
       </c>
       <c r="C19" s="0">
-        <v>2737201777</v>
+        <v>5431886078</v>
       </c>
       <c r="D19" s="0">
-        <v>198780</v>
+        <v>443782</v>
       </c>
       <c r="E19" s="0">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="F19" s="0">
-        <v>14761</v>
+        <v>54342</v>
       </c>
       <c r="G19" s="0">
-        <v>1.0700000000000001</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="H19" s="0">
-        <v>2.9900000000000002</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="I19" s="0">
-        <v>80.409999999999997</v>
+        <v>85.799999999999997</v>
       </c>
       <c r="J19" s="0">
-        <v>1067</v>
+        <v>633</v>
       </c>
       <c r="K19" s="0">
-        <v>5872.8500000000004</v>
+        <v>4184.6400000000003</v>
       </c>
       <c r="L19" s="0">
-        <v>33.799999999999997</v>
+        <v>26.489999999999998</v>
       </c>
       <c r="M19" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1004,40 +1019,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>4726136143</v>
+        <v>9007248942</v>
       </c>
       <c r="C20" s="0">
-        <v>5538368724</v>
+        <v>10781165880</v>
       </c>
       <c r="D20" s="0">
-        <v>632956</v>
+        <v>269125</v>
       </c>
       <c r="E20" s="0">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="F20" s="0">
-        <v>31851</v>
+        <v>219893</v>
       </c>
       <c r="G20" s="0">
-        <v>3.6400000000000001</v>
+        <v>5.4900000000000002</v>
       </c>
       <c r="H20" s="0">
-        <v>9.5800000000000001</v>
+        <v>8.1600000000000001</v>
       </c>
       <c r="I20" s="0">
-        <v>85.329999999999998</v>
+        <v>83.549999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>974</v>
+        <v>439</v>
       </c>
       <c r="K20" s="0">
-        <v>6007.6300000000001</v>
+        <v>3870.3600000000001</v>
       </c>
       <c r="L20" s="0">
-        <v>33.659999999999997</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="M20" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.11700000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1045,40 +1060,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>88665958114</v>
+        <v>8827043</v>
       </c>
       <c r="C21" s="0">
-        <v>101712517504</v>
+        <v>16154100</v>
       </c>
       <c r="D21" s="0">
-        <v>824652</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="F21" s="0">
-        <v>442271</v>
+        <v>198</v>
       </c>
       <c r="G21" s="0">
-        <v>3.5899999999999999</v>
+        <v>0</v>
       </c>
       <c r="H21" s="0">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="I21" s="0">
-        <v>87.170000000000002</v>
+        <v>54.640000000000001</v>
       </c>
       <c r="J21" s="0">
-        <v>1284</v>
+        <v>544</v>
       </c>
       <c r="K21" s="0">
-        <v>3803.0500000000002</v>
+        <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>21.23</v>
+        <v>0</v>
       </c>
       <c r="M21" s="0">
-        <v>0.052999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1086,40 +1101,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>533418168</v>
+        <v>89642339332</v>
       </c>
       <c r="C22" s="0">
-        <v>664032004</v>
+        <v>108026106191</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>511560</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="F22" s="0">
-        <v>2484</v>
+        <v>1118690</v>
       </c>
       <c r="G22" s="0">
-        <v>0</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>10.140000000000001</v>
       </c>
       <c r="I22" s="0">
-        <v>80.329999999999998</v>
+        <v>82.980000000000004</v>
       </c>
       <c r="J22" s="0">
-        <v>1493</v>
+        <v>684</v>
       </c>
       <c r="K22" s="0">
-        <v>4964.8400000000001</v>
+        <v>3987.8099999999999</v>
       </c>
       <c r="L22" s="0">
-        <v>27.739999999999998</v>
+        <v>28.239999999999998</v>
       </c>
       <c r="M22" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1127,40 +1142,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>47935061897</v>
+        <v>165442954314</v>
       </c>
       <c r="C23" s="0">
-        <v>54231008623</v>
+        <v>195524972924</v>
       </c>
       <c r="D23" s="0">
-        <v>820936</v>
+        <v>672508</v>
       </c>
       <c r="E23" s="0">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F23" s="0">
-        <v>184259</v>
+        <v>1086401</v>
       </c>
       <c r="G23" s="0">
-        <v>2.79</v>
+        <v>3.7400000000000002</v>
       </c>
       <c r="H23" s="0">
-        <v>10.98</v>
+        <v>10.48</v>
       </c>
       <c r="I23" s="0">
-        <v>88.390000000000001</v>
+        <v>84.609999999999999</v>
       </c>
       <c r="J23" s="0">
-        <v>1645</v>
+        <v>1079</v>
       </c>
       <c r="K23" s="0">
-        <v>4931.1099999999997</v>
+        <v>4106.1400000000003</v>
       </c>
       <c r="L23" s="0">
-        <v>27.489999999999998</v>
+        <v>24.640000000000001</v>
       </c>
       <c r="M23" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1168,40 +1183,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>11893993789</v>
+        <v>2201106780</v>
       </c>
       <c r="C24" s="0">
-        <v>13508447609</v>
+        <v>2737201777</v>
       </c>
       <c r="D24" s="0">
-        <v>1006591</v>
+        <v>198780</v>
       </c>
       <c r="E24" s="0">
-        <v>234</v>
+        <v>174</v>
       </c>
       <c r="F24" s="0">
-        <v>35352</v>
+        <v>14761</v>
       </c>
       <c r="G24" s="0">
-        <v>2.6299999999999999</v>
+        <v>1.0700000000000001</v>
       </c>
       <c r="H24" s="0">
-        <v>10.24</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="I24" s="0">
-        <v>88.049999999999997</v>
+        <v>80.409999999999997</v>
       </c>
       <c r="J24" s="0">
-        <v>1633</v>
+        <v>1067</v>
       </c>
       <c r="K24" s="0">
-        <v>5409.0799999999999</v>
+        <v>5872.8500000000004</v>
       </c>
       <c r="L24" s="0">
-        <v>23.120000000000001</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="M24" s="0">
-        <v>0.055</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="25">
@@ -1209,40 +1224,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>38983770971</v>
+        <v>4726136143</v>
       </c>
       <c r="C25" s="0">
-        <v>46295620313</v>
+        <v>5538368724</v>
       </c>
       <c r="D25" s="0">
-        <v>0</v>
+        <v>632956</v>
       </c>
       <c r="E25" s="0">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="F25" s="0">
-        <v>62231</v>
+        <v>31851</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="H25" s="0">
-        <v>0</v>
+        <v>9.5800000000000001</v>
       </c>
       <c r="I25" s="0">
-        <v>84.209999999999994</v>
+        <v>85.329999999999998</v>
       </c>
       <c r="J25" s="0">
-        <v>3486</v>
+        <v>974</v>
       </c>
       <c r="K25" s="0">
-        <v>6796.1999999999998</v>
+        <v>6007.6300000000001</v>
       </c>
       <c r="L25" s="0">
-        <v>31.859999999999999</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="M25" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="26">
@@ -1250,40 +1265,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>15381428931</v>
+        <v>88665958114</v>
       </c>
       <c r="C26" s="0">
-        <v>17997226658</v>
+        <v>101712517504</v>
       </c>
       <c r="D26" s="0">
-        <v>0</v>
+        <v>824652</v>
       </c>
       <c r="E26" s="0">
-        <v>242</v>
+        <v>179</v>
       </c>
       <c r="F26" s="0">
-        <v>20000</v>
+        <v>442271</v>
       </c>
       <c r="G26" s="0">
-        <v>0</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="H26" s="0">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="0">
-        <v>85.469999999999999</v>
+        <v>87.170000000000002</v>
       </c>
       <c r="J26" s="0">
-        <v>3725</v>
+        <v>1284</v>
       </c>
       <c r="K26" s="0">
-        <v>6753.1899999999996</v>
+        <v>3803.0500000000002</v>
       </c>
       <c r="L26" s="0">
-        <v>27.960000000000001</v>
+        <v>21.23</v>
       </c>
       <c r="M26" s="0">
-        <v>0.058999999999999997</v>
+        <v>0.052999999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1291,40 +1306,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>23791003183</v>
+        <v>533418168</v>
       </c>
       <c r="C27" s="0">
-        <v>28219020422</v>
+        <v>664032004</v>
       </c>
       <c r="D27" s="0">
-        <v>1623649</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>260</v>
+        <v>179</v>
       </c>
       <c r="F27" s="0">
-        <v>31722</v>
+        <v>2484</v>
       </c>
       <c r="G27" s="0">
-        <v>1.8300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
-        <v>13.41</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>84.310000000000002</v>
+        <v>80.329999999999998</v>
       </c>
       <c r="J27" s="0">
-        <v>3445</v>
+        <v>1493</v>
       </c>
       <c r="K27" s="0">
-        <v>7730.7700000000004</v>
+        <v>4964.8400000000001</v>
       </c>
       <c r="L27" s="0">
-        <v>29.920000000000002</v>
+        <v>27.739999999999998</v>
       </c>
       <c r="M27" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="28">
@@ -1332,40 +1347,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>22893534970</v>
+        <v>47935061897</v>
       </c>
       <c r="C28" s="0">
-        <v>26889504124</v>
+        <v>54231008623</v>
       </c>
       <c r="D28" s="0">
-        <v>1938681</v>
+        <v>820936</v>
       </c>
       <c r="E28" s="0">
-        <v>291</v>
+        <v>182</v>
       </c>
       <c r="F28" s="0">
-        <v>22537</v>
+        <v>184259</v>
       </c>
       <c r="G28" s="0">
-        <v>1.6200000000000001</v>
+        <v>2.79</v>
       </c>
       <c r="H28" s="0">
-        <v>13.869999999999999</v>
+        <v>10.98</v>
       </c>
       <c r="I28" s="0">
-        <v>85.140000000000001</v>
+        <v>88.390000000000001</v>
       </c>
       <c r="J28" s="0">
-        <v>4096</v>
+        <v>1645</v>
       </c>
       <c r="K28" s="0">
-        <v>7631.8599999999997</v>
+        <v>4931.1099999999997</v>
       </c>
       <c r="L28" s="0">
-        <v>26.199999999999999</v>
+        <v>27.489999999999998</v>
       </c>
       <c r="M28" s="0">
-        <v>0.055</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="29">
@@ -1373,40 +1388,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>847679219</v>
+        <v>11893993789</v>
       </c>
       <c r="C29" s="0">
-        <v>1013162706</v>
+        <v>13508447609</v>
       </c>
       <c r="D29" s="0">
-        <v>1608195</v>
+        <v>1006591</v>
       </c>
       <c r="E29" s="0">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="F29" s="0">
-        <v>680</v>
+        <v>35352</v>
       </c>
       <c r="G29" s="0">
-        <v>1.0800000000000001</v>
+        <v>2.6299999999999999</v>
       </c>
       <c r="H29" s="0">
-        <v>11.789999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="I29" s="0">
-        <v>83.670000000000002</v>
+        <v>88.049999999999997</v>
       </c>
       <c r="J29" s="0">
-        <v>5315</v>
+        <v>1633</v>
       </c>
       <c r="K29" s="0">
-        <v>6881.9399999999996</v>
+        <v>5409.0799999999999</v>
       </c>
       <c r="L29" s="0">
-        <v>24.550000000000001</v>
+        <v>23.120000000000001</v>
       </c>
       <c r="M29" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="30">
@@ -1414,40 +1429,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>9566236554</v>
+        <v>38983770971</v>
       </c>
       <c r="C30" s="0">
-        <v>11200460405</v>
+        <v>46295620313</v>
       </c>
       <c r="D30" s="0">
-        <v>2408701</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="F30" s="0">
-        <v>5980</v>
+        <v>62231</v>
       </c>
       <c r="G30" s="0">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="H30" s="0">
-        <v>15.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
-        <v>85.409999999999997</v>
+        <v>84.209999999999994</v>
       </c>
       <c r="J30" s="0">
-        <v>6139</v>
+        <v>3486</v>
       </c>
       <c r="K30" s="0">
-        <v>7491.8299999999999</v>
+        <v>6796.1999999999998</v>
       </c>
       <c r="L30" s="0">
-        <v>24.559999999999999</v>
+        <v>31.859999999999999</v>
       </c>
       <c r="M30" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="31">
@@ -1455,40 +1470,40 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>13046758010</v>
+        <v>15381428931</v>
       </c>
       <c r="C31" s="0">
-        <v>15577601393</v>
+        <v>17997226658</v>
       </c>
       <c r="D31" s="0">
-        <v>1492107</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F31" s="0">
-        <v>17686</v>
+        <v>20000</v>
       </c>
       <c r="G31" s="0">
-        <v>1.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>13.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>83.75</v>
+        <v>85.469999999999999</v>
       </c>
       <c r="J31" s="0">
-        <v>3883</v>
+        <v>3725</v>
       </c>
       <c r="K31" s="0">
-        <v>8280.1499999999996</v>
+        <v>6753.1899999999996</v>
       </c>
       <c r="L31" s="0">
-        <v>36.479999999999997</v>
+        <v>27.960000000000001</v>
       </c>
       <c r="M31" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.058999999999999997</v>
       </c>
     </row>
     <row r="32">
@@ -1496,37 +1511,37 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>27220559776</v>
+        <v>23791003183</v>
       </c>
       <c r="C32" s="0">
-        <v>32692611730</v>
+        <v>28219020422</v>
       </c>
       <c r="D32" s="0">
-        <v>2094338</v>
+        <v>1623649</v>
       </c>
       <c r="E32" s="0">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F32" s="0">
-        <v>21800</v>
+        <v>31722</v>
       </c>
       <c r="G32" s="0">
-        <v>1.3999999999999999</v>
+        <v>1.8300000000000001</v>
       </c>
       <c r="H32" s="0">
-        <v>15.460000000000001</v>
+        <v>13.41</v>
       </c>
       <c r="I32" s="0">
-        <v>83.260000000000005</v>
+        <v>84.310000000000002</v>
       </c>
       <c r="J32" s="0">
-        <v>5651</v>
+        <v>3445</v>
       </c>
       <c r="K32" s="0">
-        <v>8692.1399999999994</v>
+        <v>7730.7700000000004</v>
       </c>
       <c r="L32" s="0">
-        <v>32.719999999999999</v>
+        <v>29.920000000000002</v>
       </c>
       <c r="M32" s="0">
         <v>0.064000000000000001</v>
@@ -1537,40 +1552,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>4782436290</v>
+        <v>22893534970</v>
       </c>
       <c r="C33" s="0">
-        <v>5372651340</v>
+        <v>26889504124</v>
       </c>
       <c r="D33" s="0">
-        <v>0</v>
+        <v>1938681</v>
       </c>
       <c r="E33" s="0">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="F33" s="0">
-        <v>4977</v>
+        <v>22537</v>
       </c>
       <c r="G33" s="0">
-        <v>0</v>
+        <v>1.6200000000000001</v>
       </c>
       <c r="H33" s="0">
-        <v>0</v>
+        <v>13.869999999999999</v>
       </c>
       <c r="I33" s="0">
-        <v>89.010000000000005</v>
+        <v>85.140000000000001</v>
       </c>
       <c r="J33" s="0">
-        <v>3395</v>
+        <v>4096</v>
       </c>
       <c r="K33" s="0">
-        <v>5578.6599999999999</v>
+        <v>7631.8599999999997</v>
       </c>
       <c r="L33" s="0">
-        <v>17.539999999999999</v>
+        <v>26.199999999999999</v>
       </c>
       <c r="M33" s="0">
-        <v>0.035999999999999997</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="34">
@@ -1578,40 +1593,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>71307801505</v>
+        <v>847679219</v>
       </c>
       <c r="C34" s="0">
-        <v>85462342476</v>
+        <v>1013162706</v>
       </c>
       <c r="D34" s="0">
-        <v>1783066</v>
+        <v>1608195</v>
       </c>
       <c r="E34" s="0">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F34" s="0">
-        <v>72294</v>
+        <v>680</v>
       </c>
       <c r="G34" s="0">
-        <v>1.51</v>
+        <v>1.0800000000000001</v>
       </c>
       <c r="H34" s="0">
-        <v>12.699999999999999</v>
+        <v>11.789999999999999</v>
       </c>
       <c r="I34" s="0">
-        <v>83.439999999999998</v>
+        <v>83.670000000000002</v>
       </c>
       <c r="J34" s="0">
-        <v>4141</v>
+        <v>5315</v>
       </c>
       <c r="K34" s="0">
-        <v>9419.4699999999993</v>
+        <v>6881.9399999999996</v>
       </c>
       <c r="L34" s="0">
-        <v>32.920000000000002</v>
+        <v>24.550000000000001</v>
       </c>
       <c r="M34" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="35">
@@ -1619,40 +1634,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>24695859448</v>
+        <v>9566236554</v>
       </c>
       <c r="C35" s="0">
-        <v>29615257922</v>
+        <v>11200460405</v>
       </c>
       <c r="D35" s="0">
-        <v>0</v>
+        <v>2408701</v>
       </c>
       <c r="E35" s="0">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="F35" s="0">
-        <v>16559</v>
+        <v>5980</v>
       </c>
       <c r="G35" s="0">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="H35" s="0">
-        <v>0</v>
+        <v>15.470000000000001</v>
       </c>
       <c r="I35" s="0">
-        <v>83.390000000000001</v>
+        <v>85.409999999999997</v>
       </c>
       <c r="J35" s="0">
-        <v>5462</v>
+        <v>6139</v>
       </c>
       <c r="K35" s="0">
-        <v>10818.790000000001</v>
+        <v>7491.8299999999999</v>
       </c>
       <c r="L35" s="0">
-        <v>33.07</v>
+        <v>24.559999999999999</v>
       </c>
       <c r="M35" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1660,40 +1675,245 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>1029487377138</v>
+        <v>13046758010</v>
       </c>
       <c r="C36" s="0">
-        <v>1215788509319</v>
+        <v>15577601393</v>
       </c>
       <c r="D36" s="0">
-        <v>0</v>
+        <v>1492107</v>
       </c>
       <c r="E36" s="0">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="F36" s="0">
-        <v>7998601</v>
+        <v>17686</v>
       </c>
       <c r="G36" s="0">
-        <v>0</v>
+        <v>1.6899999999999999</v>
       </c>
       <c r="H36" s="0">
-        <v>0</v>
+        <v>13.380000000000001</v>
       </c>
       <c r="I36" s="0">
-        <v>84.680000000000007</v>
+        <v>83.75</v>
       </c>
       <c r="J36" s="0">
-        <v>936</v>
+        <v>3883</v>
       </c>
       <c r="K36" s="0">
-        <v>3960.2600000000002</v>
+        <v>8280.1499999999996</v>
       </c>
       <c r="L36" s="0">
-        <v>25.91</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="M36" s="0">
+        <v>0.073999999999999996</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
+        <v>27220559776</v>
+      </c>
+      <c r="C37" s="0">
+        <v>32692611730</v>
+      </c>
+      <c r="D37" s="0">
+        <v>2094338</v>
+      </c>
+      <c r="E37" s="0">
+        <v>267</v>
+      </c>
+      <c r="F37" s="0">
+        <v>21800</v>
+      </c>
+      <c r="G37" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H37" s="0">
+        <v>15.460000000000001</v>
+      </c>
+      <c r="I37" s="0">
+        <v>83.260000000000005</v>
+      </c>
+      <c r="J37" s="0">
+        <v>5651</v>
+      </c>
+      <c r="K37" s="0">
+        <v>8692.1399999999994</v>
+      </c>
+      <c r="L37" s="0">
+        <v>32.719999999999999</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>4782436290</v>
+      </c>
+      <c r="C38" s="0">
+        <v>5372651340</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0">
+        <v>318</v>
+      </c>
+      <c r="F38" s="0">
+        <v>4977</v>
+      </c>
+      <c r="G38" s="0">
+        <v>0</v>
+      </c>
+      <c r="H38" s="0">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0">
+        <v>89.010000000000005</v>
+      </c>
+      <c r="J38" s="0">
+        <v>3395</v>
+      </c>
+      <c r="K38" s="0">
+        <v>5578.6599999999999</v>
+      </c>
+      <c r="L38" s="0">
+        <v>17.539999999999999</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.035999999999999997</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>71307801505</v>
+      </c>
+      <c r="C39" s="0">
+        <v>85462342476</v>
+      </c>
+      <c r="D39" s="0">
+        <v>1783066</v>
+      </c>
+      <c r="E39" s="0">
+        <v>293</v>
+      </c>
+      <c r="F39" s="0">
+        <v>72294</v>
+      </c>
+      <c r="G39" s="0">
+        <v>1.51</v>
+      </c>
+      <c r="H39" s="0">
+        <v>12.699999999999999</v>
+      </c>
+      <c r="I39" s="0">
+        <v>83.439999999999998</v>
+      </c>
+      <c r="J39" s="0">
+        <v>4141</v>
+      </c>
+      <c r="K39" s="0">
+        <v>9419.4699999999993</v>
+      </c>
+      <c r="L39" s="0">
+        <v>32.920000000000002</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0">
+        <v>24695859448</v>
+      </c>
+      <c r="C40" s="0">
+        <v>29615257922</v>
+      </c>
+      <c r="D40" s="0">
+        <v>0</v>
+      </c>
+      <c r="E40" s="0">
+        <v>325</v>
+      </c>
+      <c r="F40" s="0">
+        <v>16559</v>
+      </c>
+      <c r="G40" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" s="0">
+        <v>0</v>
+      </c>
+      <c r="I40" s="0">
+        <v>83.390000000000001</v>
+      </c>
+      <c r="J40" s="0">
+        <v>5462</v>
+      </c>
+      <c r="K40" s="0">
+        <v>10818.790000000001</v>
+      </c>
+      <c r="L40" s="0">
+        <v>33.07</v>
+      </c>
+      <c r="M40" s="0">
         <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0">
+        <v>1046062680824</v>
+      </c>
+      <c r="C41" s="0">
+        <v>1235537403983</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0">
+        <v>131</v>
+      </c>
+      <c r="F41" s="0">
+        <v>8398644</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0">
+        <v>84.659999999999997</v>
+      </c>
+      <c r="J41" s="0">
+        <v>911</v>
+      </c>
+      <c r="K41" s="0">
+        <v>3935.23</v>
+      </c>
+      <c r="L41" s="0">
+        <v>25.949999999999999</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0.067000000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Aircraft_Cumulative_Statistics_2019.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Aircraft_Cumulative_Statistics_2019.xlsx
@@ -13,41 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="42">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E140</t>
-  </si>
-  <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>Q400</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
     <t>E190</t>
   </si>
   <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -57,9 +30,6 @@
     <t>A320</t>
   </si>
   <si>
-    <t>A320NEO</t>
-  </si>
-  <si>
     <t>A321</t>
   </si>
   <si>
@@ -73,9 +43,6 @@
   </si>
   <si>
     <t>B717-200</t>
-  </si>
-  <si>
-    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -217,7 +184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -240,40 +207,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2">
@@ -281,40 +248,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1289199017</v>
+        <v>1011539795</v>
       </c>
       <c r="C2" s="0">
-        <v>1680885599</v>
+        <v>1293269433</v>
       </c>
       <c r="D2" s="0">
-        <v>30927</v>
+        <v>206923</v>
       </c>
       <c r="E2" s="0">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>104370</v>
+        <v>32122</v>
       </c>
       <c r="G2" s="0">
-        <v>1.9199999999999999</v>
+        <v>5.1399999999999997</v>
       </c>
       <c r="H2" s="0">
-        <v>2.9100000000000001</v>
+        <v>8.3599999999999994</v>
       </c>
       <c r="I2" s="0">
-        <v>76.700000000000003</v>
+        <v>78.219999999999999</v>
       </c>
       <c r="J2" s="0">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="K2" s="0">
-        <v>1292.3699999999999</v>
+        <v>2395.0900000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>29.370000000000001</v>
+        <v>24.190000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.122</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -322,40 +289,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>4152009552</v>
+        <v>1768271368</v>
       </c>
       <c r="C3" s="0">
-        <v>5149508147</v>
+        <v>2099179520</v>
       </c>
       <c r="D3" s="0">
-        <v>84142</v>
+        <v>338032</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F3" s="0">
-        <v>298913</v>
+        <v>20023</v>
       </c>
       <c r="G3" s="0">
-        <v>4.8799999999999999</v>
+        <v>3.2200000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>7.29</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="I3" s="0">
-        <v>80.629999999999995</v>
+        <v>84.239999999999995</v>
       </c>
       <c r="J3" s="0">
-        <v>345</v>
+        <v>962</v>
       </c>
       <c r="K3" s="0">
-        <v>516.5</v>
+        <v>3523.9099999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>10.33</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="M3" s="0">
-        <v>0.044999999999999998</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="4">
@@ -363,40 +330,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>7084744886</v>
+        <v>33485519062</v>
       </c>
       <c r="C4" s="0">
-        <v>8915925051</v>
+        <v>39594275999</v>
       </c>
       <c r="D4" s="0">
-        <v>96828</v>
+        <v>435485</v>
       </c>
       <c r="E4" s="0">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="F4" s="0">
-        <v>491979</v>
+        <v>369220</v>
       </c>
       <c r="G4" s="0">
-        <v>5.3399999999999999</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="H4" s="0">
-        <v>7.7699999999999996</v>
+        <v>9.5899999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>79.459999999999994</v>
+        <v>84.569999999999993</v>
       </c>
       <c r="J4" s="0">
-        <v>362</v>
+        <v>832</v>
       </c>
       <c r="K4" s="0">
-        <v>1504</v>
+        <v>3769.6900000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>30.079999999999998</v>
+        <v>29.260000000000002</v>
       </c>
       <c r="M4" s="0">
-        <v>0.121</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="5">
@@ -404,40 +371,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>3281730300</v>
+        <v>33739432000</v>
       </c>
       <c r="C5" s="0">
-        <v>4177037267</v>
+        <v>39670782868</v>
       </c>
       <c r="D5" s="0">
-        <v>191783</v>
+        <v>603266</v>
       </c>
       <c r="E5" s="0">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="F5" s="0">
-        <v>100474</v>
+        <v>289610</v>
       </c>
       <c r="G5" s="0">
-        <v>4.6100000000000003</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H5" s="0">
-        <v>9.4100000000000001</v>
+        <v>11.029999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>78.569999999999993</v>
+        <v>85.049999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>596</v>
+        <v>901</v>
       </c>
       <c r="K5" s="0">
-        <v>1406.8399999999999</v>
+        <v>4147.3699999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>20.190000000000001</v>
+        <v>27.280000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="6">
@@ -445,40 +412,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>28646500192</v>
+        <v>74511329454</v>
       </c>
       <c r="C6" s="0">
-        <v>35802849695</v>
+        <v>84183613420</v>
       </c>
       <c r="D6" s="0">
-        <v>189573</v>
+        <v>758479</v>
       </c>
       <c r="E6" s="0">
-        <v>76</v>
+        <v>184</v>
       </c>
       <c r="F6" s="0">
-        <v>730599</v>
+        <v>387411</v>
       </c>
       <c r="G6" s="0">
-        <v>3.8700000000000001</v>
+        <v>3.4900000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>7.9800000000000004</v>
+        <v>10.83</v>
       </c>
       <c r="I6" s="0">
-        <v>80.010000000000005</v>
+        <v>88.510000000000005</v>
       </c>
       <c r="J6" s="0">
-        <v>648</v>
+        <v>1202</v>
       </c>
       <c r="K6" s="0">
-        <v>1297.4100000000001</v>
+        <v>4951.6599999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>17.16</v>
+        <v>27.309999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.055</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="7">
@@ -486,40 +453,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>1170303614</v>
+        <v>1036095305</v>
       </c>
       <c r="C7" s="0">
-        <v>1493766700</v>
+        <v>1193263656</v>
       </c>
       <c r="D7" s="0">
-        <v>118930</v>
+        <v>407257</v>
       </c>
       <c r="E7" s="0">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="F7" s="0">
-        <v>79994</v>
+        <v>3716</v>
       </c>
       <c r="G7" s="0">
-        <v>6.3700000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="H7" s="0">
-        <v>7.4299999999999997</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="I7" s="0">
-        <v>78.349999999999994</v>
+        <v>86.829999999999998</v>
       </c>
       <c r="J7" s="0">
-        <v>246</v>
+        <v>1639</v>
       </c>
       <c r="K7" s="0">
-        <v>1979.3199999999999</v>
+        <v>6626.7299999999996</v>
       </c>
       <c r="L7" s="0">
-        <v>26.039999999999999</v>
+        <v>33.82</v>
       </c>
       <c r="M7" s="0">
-        <v>0.124</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -527,40 +494,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>66359511</v>
+        <v>9446378986</v>
       </c>
       <c r="C8" s="0">
-        <v>83292450</v>
+        <v>11126202187</v>
       </c>
       <c r="D8" s="0">
-        <v>55528</v>
+        <v>356495</v>
       </c>
       <c r="E8" s="0">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="F8" s="0">
-        <v>4609</v>
+        <v>161139</v>
       </c>
       <c r="G8" s="0">
-        <v>3.0699999999999998</v>
+        <v>5.1600000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>4.6900000000000004</v>
+        <v>8.0999999999999996</v>
       </c>
       <c r="I8" s="0">
-        <v>79.670000000000002</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="J8" s="0">
-        <v>361</v>
+        <v>470</v>
       </c>
       <c r="K8" s="0">
-        <v>1270.29</v>
+        <v>4208.2200000000003</v>
       </c>
       <c r="L8" s="0">
-        <v>25.41</v>
+        <v>28.620000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.107</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="9">
@@ -568,40 +535,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>10043560726</v>
+        <v>4660595026</v>
       </c>
       <c r="C9" s="0">
-        <v>12609704137</v>
+        <v>5431886078</v>
       </c>
       <c r="D9" s="0">
-        <v>155675</v>
+        <v>443782</v>
       </c>
       <c r="E9" s="0">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="F9" s="0">
-        <v>401212</v>
+        <v>54342</v>
       </c>
       <c r="G9" s="0">
-        <v>4.9500000000000002</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="H9" s="0">
-        <v>8.2599999999999998</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="I9" s="0">
-        <v>79.650000000000006</v>
+        <v>85.799999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>462</v>
+        <v>633</v>
       </c>
       <c r="K9" s="0">
-        <v>1290.8900000000001</v>
+        <v>4184.6400000000003</v>
       </c>
       <c r="L9" s="0">
-        <v>19.010000000000002</v>
+        <v>26.489999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -609,40 +576,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>6235219049</v>
+        <v>8178351437</v>
       </c>
       <c r="C10" s="0">
-        <v>7732527333</v>
+        <v>9654043704</v>
       </c>
       <c r="D10" s="0">
-        <v>274690</v>
+        <v>294690</v>
       </c>
       <c r="E10" s="0">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F10" s="0">
-        <v>149363</v>
+        <v>156199</v>
       </c>
       <c r="G10" s="0">
-        <v>5.3099999999999996</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H10" s="0">
-        <v>9.4299999999999997</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="I10" s="0">
-        <v>80.640000000000001</v>
+        <v>84.709999999999994</v>
       </c>
       <c r="J10" s="0">
-        <v>519</v>
+        <v>562</v>
       </c>
       <c r="K10" s="0">
-        <v>3551</v>
+        <v>3747.3000000000002</v>
       </c>
       <c r="L10" s="0">
-        <v>35.579999999999998</v>
+        <v>34.07</v>
       </c>
       <c r="M10" s="0">
-        <v>0.122</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="11">
@@ -650,40 +617,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>16001537037</v>
+        <v>7084892407</v>
       </c>
       <c r="C11" s="0">
-        <v>19890971885</v>
+        <v>8451773012</v>
       </c>
       <c r="D11" s="0">
-        <v>205634</v>
+        <v>461846</v>
       </c>
       <c r="E11" s="0">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="F11" s="0">
-        <v>523996</v>
+        <v>63219</v>
       </c>
       <c r="G11" s="0">
-        <v>5.4199999999999999</v>
+        <v>3.4500000000000002</v>
       </c>
       <c r="H11" s="0">
-        <v>9.3699999999999992</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="I11" s="0">
-        <v>80.450000000000003</v>
+        <v>83.829999999999998</v>
       </c>
       <c r="J11" s="0">
-        <v>499</v>
+        <v>1064</v>
       </c>
       <c r="K11" s="0">
-        <v>1138.7</v>
+        <v>4133.1700000000001</v>
       </c>
       <c r="L11" s="0">
-        <v>14.960000000000001</v>
+        <v>32.899999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="12">
@@ -691,40 +658,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>1768271368</v>
+        <v>98317252792</v>
       </c>
       <c r="C12" s="0">
-        <v>2099179520</v>
+        <v>115456937047</v>
       </c>
       <c r="D12" s="0">
-        <v>338032</v>
+        <v>629880</v>
       </c>
       <c r="E12" s="0">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="F12" s="0">
-        <v>20023</v>
+        <v>666812</v>
       </c>
       <c r="G12" s="0">
-        <v>3.2200000000000002</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>8.7300000000000004</v>
+        <v>10.27</v>
       </c>
       <c r="I12" s="0">
-        <v>84.239999999999995</v>
+        <v>85.150000000000006</v>
       </c>
       <c r="J12" s="0">
-        <v>962</v>
+        <v>1061</v>
       </c>
       <c r="K12" s="0">
-        <v>3523.9099999999999</v>
+        <v>4402.0699999999997</v>
       </c>
       <c r="L12" s="0">
-        <v>32.340000000000003</v>
+        <v>26.969999999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="13">
@@ -732,40 +699,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>50295438770</v>
+        <v>902639686</v>
       </c>
       <c r="C13" s="0">
-        <v>59319937722</v>
+        <v>1096442552</v>
       </c>
       <c r="D13" s="0">
-        <v>489479</v>
+        <v>726121</v>
       </c>
       <c r="E13" s="0">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="F13" s="0">
-        <v>508792</v>
+        <v>5324</v>
       </c>
       <c r="G13" s="0">
-        <v>4.2000000000000002</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="H13" s="0">
-        <v>10.16</v>
+        <v>11.130000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>84.790000000000006</v>
+        <v>82.319999999999993</v>
       </c>
       <c r="J13" s="0">
-        <v>868</v>
+        <v>1197</v>
       </c>
       <c r="K13" s="0">
-        <v>3504.0799999999999</v>
+        <v>4706.96</v>
       </c>
       <c r="L13" s="0">
-        <v>26.149999999999999</v>
+        <v>27.370000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="14">
@@ -773,40 +740,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>97547997188</v>
+        <v>2412509151</v>
       </c>
       <c r="C14" s="0">
-        <v>115846730618</v>
+        <v>2799491980</v>
       </c>
       <c r="D14" s="0">
-        <v>650349</v>
+        <v>640616</v>
       </c>
       <c r="E14" s="0">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F14" s="0">
-        <v>714600</v>
+        <v>15540</v>
       </c>
       <c r="G14" s="0">
-        <v>4.0099999999999998</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>10.82</v>
+        <v>9.4399999999999995</v>
       </c>
       <c r="I14" s="0">
-        <v>84.200000000000003</v>
+        <v>86.180000000000007</v>
       </c>
       <c r="J14" s="0">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="K14" s="0">
-        <v>4156.4899999999998</v>
+        <v>7889.9799999999996</v>
       </c>
       <c r="L14" s="0">
-        <v>25.969999999999999</v>
+        <v>44.079999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.11600000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -814,40 +781,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>13854235199</v>
+        <v>66908080936</v>
       </c>
       <c r="C15" s="0">
-        <v>16210513742</v>
+        <v>76322462758</v>
       </c>
       <c r="D15" s="0">
-        <v>796977</v>
+        <v>800865</v>
       </c>
       <c r="E15" s="0">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F15" s="0">
-        <v>83764</v>
+        <v>352210</v>
       </c>
       <c r="G15" s="0">
-        <v>4.1200000000000001</v>
+        <v>3.7000000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>11.49</v>
+        <v>11.34</v>
       </c>
       <c r="I15" s="0">
-        <v>85.459999999999994</v>
+        <v>87.659999999999997</v>
       </c>
       <c r="J15" s="0">
-        <v>1045</v>
+        <v>1207</v>
       </c>
       <c r="K15" s="0">
-        <v>3733.4699999999998</v>
+        <v>3990.5799999999999</v>
       </c>
       <c r="L15" s="0">
-        <v>20.170000000000002</v>
+        <v>22.239999999999998</v>
       </c>
       <c r="M15" s="0">
-        <v>0.053999999999999999</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -855,40 +822,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>111293552706</v>
+        <v>533418168</v>
       </c>
       <c r="C16" s="0">
-        <v>127141389815</v>
+        <v>664032004</v>
       </c>
       <c r="D16" s="0">
-        <v>816842</v>
+        <v>522860</v>
       </c>
       <c r="E16" s="0">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F16" s="0">
-        <v>538431</v>
+        <v>2484</v>
       </c>
       <c r="G16" s="0">
-        <v>3.46</v>
+        <v>1.96</v>
       </c>
       <c r="H16" s="0">
-        <v>11.220000000000001</v>
+        <v>7.1100000000000003</v>
       </c>
       <c r="I16" s="0">
-        <v>87.540000000000006</v>
+        <v>80.329999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>1271</v>
+        <v>1493</v>
       </c>
       <c r="K16" s="0">
-        <v>4593.5799999999999</v>
+        <v>4964.8400000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>24.620000000000001</v>
+        <v>27.739999999999998</v>
       </c>
       <c r="M16" s="0">
-        <v>0.063</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="17">
@@ -896,40 +863,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>6650934318</v>
+        <v>47935061897</v>
       </c>
       <c r="C17" s="0">
-        <v>7749661212</v>
+        <v>54231008623</v>
       </c>
       <c r="D17" s="0">
-        <v>707086</v>
+        <v>820936</v>
       </c>
       <c r="E17" s="0">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F17" s="0">
-        <v>19418</v>
+        <v>184259</v>
       </c>
       <c r="G17" s="0">
-        <v>1.77</v>
+        <v>2.79</v>
       </c>
       <c r="H17" s="0">
-        <v>8.6199999999999992</v>
+        <v>10.98</v>
       </c>
       <c r="I17" s="0">
-        <v>85.819999999999993</v>
+        <v>88.390000000000001</v>
       </c>
       <c r="J17" s="0">
-        <v>2105</v>
+        <v>1645</v>
       </c>
       <c r="K17" s="0">
-        <v>4791.8000000000002</v>
+        <v>4931.1099999999997</v>
       </c>
       <c r="L17" s="0">
-        <v>25.27</v>
+        <v>27.489999999999998</v>
       </c>
       <c r="M17" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="18">
@@ -937,40 +904,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>9446378986</v>
+        <v>11893993789</v>
       </c>
       <c r="C18" s="0">
-        <v>11126202187</v>
+        <v>13508447609</v>
       </c>
       <c r="D18" s="0">
-        <v>356495</v>
+        <v>1006591</v>
       </c>
       <c r="E18" s="0">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="F18" s="0">
-        <v>161139</v>
+        <v>35352</v>
       </c>
       <c r="G18" s="0">
-        <v>5.1600000000000001</v>
+        <v>2.6299999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>8.0999999999999996</v>
+        <v>10.24</v>
       </c>
       <c r="I18" s="0">
-        <v>84.900000000000006</v>
+        <v>88.049999999999997</v>
       </c>
       <c r="J18" s="0">
-        <v>470</v>
+        <v>1633</v>
       </c>
       <c r="K18" s="0">
-        <v>4208.2200000000003</v>
+        <v>5409.0799999999999</v>
       </c>
       <c r="L18" s="0">
-        <v>28.620000000000001</v>
+        <v>23.120000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.096000000000000002</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="19">
@@ -978,40 +945,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>4660595026</v>
+        <v>38967115362</v>
       </c>
       <c r="C19" s="0">
-        <v>5431886078</v>
+        <v>46276966289</v>
       </c>
       <c r="D19" s="0">
-        <v>443782</v>
+        <v>1143488</v>
       </c>
       <c r="E19" s="0">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="F19" s="0">
-        <v>54342</v>
+        <v>62202</v>
       </c>
       <c r="G19" s="0">
-        <v>4.4400000000000004</v>
+        <v>1.54</v>
       </c>
       <c r="H19" s="0">
-        <v>8.3800000000000008</v>
+        <v>11.42</v>
       </c>
       <c r="I19" s="0">
-        <v>85.799999999999997</v>
+        <v>84.200000000000003</v>
       </c>
       <c r="J19" s="0">
-        <v>633</v>
+        <v>3486</v>
       </c>
       <c r="K19" s="0">
-        <v>4184.6400000000003</v>
+        <v>6785.3000000000002</v>
       </c>
       <c r="L19" s="0">
-        <v>26.489999999999998</v>
+        <v>31.809999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="20">
@@ -1019,40 +986,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>9007248942</v>
+        <v>15381428931</v>
       </c>
       <c r="C20" s="0">
-        <v>10781165880</v>
+        <v>17997226658</v>
       </c>
       <c r="D20" s="0">
-        <v>269125</v>
+        <v>1341075</v>
       </c>
       <c r="E20" s="0">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="F20" s="0">
-        <v>219893</v>
+        <v>20000</v>
       </c>
       <c r="G20" s="0">
-        <v>5.4900000000000002</v>
+        <v>1.49</v>
       </c>
       <c r="H20" s="0">
-        <v>8.1600000000000001</v>
+        <v>11.67</v>
       </c>
       <c r="I20" s="0">
-        <v>83.549999999999997</v>
+        <v>85.469999999999999</v>
       </c>
       <c r="J20" s="0">
-        <v>439</v>
+        <v>3725</v>
       </c>
       <c r="K20" s="0">
-        <v>3870.3600000000001</v>
+        <v>6753.1899999999996</v>
       </c>
       <c r="L20" s="0">
-        <v>34.380000000000003</v>
+        <v>27.960000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.11700000000000001</v>
+        <v>0.058999999999999997</v>
       </c>
     </row>
     <row r="21">
@@ -1060,40 +1027,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>8827043</v>
+        <v>10521705796</v>
       </c>
       <c r="C21" s="0">
-        <v>16154100</v>
+        <v>13023903490</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>1510894</v>
       </c>
       <c r="E21" s="0">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="F21" s="0">
-        <v>198</v>
+        <v>15131</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>13.449999999999999</v>
       </c>
       <c r="I21" s="0">
-        <v>54.640000000000001</v>
+        <v>80.790000000000006</v>
       </c>
       <c r="J21" s="0">
-        <v>544</v>
+        <v>3610</v>
       </c>
       <c r="K21" s="0">
-        <v>0</v>
+        <v>7926.0100000000002</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>33.219999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="22">
@@ -1101,40 +1068,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>89642339332</v>
+        <v>22893534970</v>
       </c>
       <c r="C22" s="0">
-        <v>108026106191</v>
+        <v>26889504124</v>
       </c>
       <c r="D22" s="0">
-        <v>511560</v>
+        <v>1938681</v>
       </c>
       <c r="E22" s="0">
-        <v>142</v>
+        <v>291</v>
       </c>
       <c r="F22" s="0">
-        <v>1118690</v>
+        <v>22537</v>
       </c>
       <c r="G22" s="0">
-        <v>5.2999999999999998</v>
+        <v>1.6200000000000001</v>
       </c>
       <c r="H22" s="0">
-        <v>10.140000000000001</v>
+        <v>13.869999999999999</v>
       </c>
       <c r="I22" s="0">
-        <v>82.980000000000004</v>
+        <v>85.140000000000001</v>
       </c>
       <c r="J22" s="0">
-        <v>684</v>
+        <v>4096</v>
       </c>
       <c r="K22" s="0">
-        <v>3987.8099999999999</v>
+        <v>7631.8599999999997</v>
       </c>
       <c r="L22" s="0">
-        <v>28.239999999999998</v>
+        <v>26.199999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="23">
@@ -1142,40 +1109,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>165442954314</v>
+        <v>847679219</v>
       </c>
       <c r="C23" s="0">
-        <v>195524972924</v>
+        <v>1013162706</v>
       </c>
       <c r="D23" s="0">
-        <v>672508</v>
+        <v>1608195</v>
       </c>
       <c r="E23" s="0">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="F23" s="0">
-        <v>1086401</v>
+        <v>680</v>
       </c>
       <c r="G23" s="0">
-        <v>3.7400000000000002</v>
+        <v>1.0800000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>10.48</v>
+        <v>11.789999999999999</v>
       </c>
       <c r="I23" s="0">
-        <v>84.609999999999999</v>
+        <v>83.670000000000002</v>
       </c>
       <c r="J23" s="0">
-        <v>1079</v>
+        <v>5315</v>
       </c>
       <c r="K23" s="0">
-        <v>4106.1400000000003</v>
+        <v>6881.9399999999996</v>
       </c>
       <c r="L23" s="0">
-        <v>24.640000000000001</v>
+        <v>24.550000000000001</v>
       </c>
       <c r="M23" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="24">
@@ -1183,40 +1150,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>2201106780</v>
+        <v>9566236554</v>
       </c>
       <c r="C24" s="0">
-        <v>2737201777</v>
+        <v>11200460405</v>
       </c>
       <c r="D24" s="0">
-        <v>198780</v>
+        <v>2408701</v>
       </c>
       <c r="E24" s="0">
-        <v>174</v>
+        <v>305</v>
       </c>
       <c r="F24" s="0">
-        <v>14761</v>
+        <v>5980</v>
       </c>
       <c r="G24" s="0">
-        <v>1.0700000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="H24" s="0">
-        <v>2.9900000000000002</v>
+        <v>15.470000000000001</v>
       </c>
       <c r="I24" s="0">
-        <v>80.409999999999997</v>
+        <v>85.409999999999997</v>
       </c>
       <c r="J24" s="0">
-        <v>1067</v>
+        <v>6139</v>
       </c>
       <c r="K24" s="0">
-        <v>5872.8500000000004</v>
+        <v>7491.8299999999999</v>
       </c>
       <c r="L24" s="0">
-        <v>33.799999999999997</v>
+        <v>24.559999999999999</v>
       </c>
       <c r="M24" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1224,40 +1191,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>4726136143</v>
+        <v>13046758010</v>
       </c>
       <c r="C25" s="0">
-        <v>5538368724</v>
+        <v>15577601393</v>
       </c>
       <c r="D25" s="0">
-        <v>632956</v>
+        <v>1492107</v>
       </c>
       <c r="E25" s="0">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="F25" s="0">
-        <v>31851</v>
+        <v>17686</v>
       </c>
       <c r="G25" s="0">
-        <v>3.6400000000000001</v>
+        <v>1.6899999999999999</v>
       </c>
       <c r="H25" s="0">
-        <v>9.5800000000000001</v>
+        <v>13.380000000000001</v>
       </c>
       <c r="I25" s="0">
-        <v>85.329999999999998</v>
+        <v>83.75</v>
       </c>
       <c r="J25" s="0">
-        <v>974</v>
+        <v>3883</v>
       </c>
       <c r="K25" s="0">
-        <v>6007.6300000000001</v>
+        <v>8280.1499999999996</v>
       </c>
       <c r="L25" s="0">
-        <v>33.659999999999997</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="M25" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="26">
@@ -1265,40 +1232,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>88665958114</v>
+        <v>27220559776</v>
       </c>
       <c r="C26" s="0">
-        <v>101712517504</v>
+        <v>32692611730</v>
       </c>
       <c r="D26" s="0">
-        <v>824652</v>
+        <v>2094338</v>
       </c>
       <c r="E26" s="0">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="F26" s="0">
-        <v>442271</v>
+        <v>21800</v>
       </c>
       <c r="G26" s="0">
-        <v>3.5899999999999999</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="H26" s="0">
-        <v>11.6</v>
+        <v>15.460000000000001</v>
       </c>
       <c r="I26" s="0">
-        <v>87.170000000000002</v>
+        <v>83.260000000000005</v>
       </c>
       <c r="J26" s="0">
-        <v>1284</v>
+        <v>5651</v>
       </c>
       <c r="K26" s="0">
-        <v>3803.0500000000002</v>
+        <v>8692.1399999999994</v>
       </c>
       <c r="L26" s="0">
-        <v>21.23</v>
+        <v>32.719999999999999</v>
       </c>
       <c r="M26" s="0">
-        <v>0.052999999999999999</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1306,40 +1273,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>533418168</v>
+        <v>4782436290</v>
       </c>
       <c r="C27" s="0">
-        <v>664032004</v>
+        <v>5372651340</v>
       </c>
       <c r="D27" s="0">
-        <v>0</v>
+        <v>2377279</v>
       </c>
       <c r="E27" s="0">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="F27" s="0">
-        <v>2484</v>
+        <v>4977</v>
       </c>
       <c r="G27" s="0">
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H27" s="0">
-        <v>0</v>
+        <v>15.449999999999999</v>
       </c>
       <c r="I27" s="0">
-        <v>80.329999999999998</v>
+        <v>89.010000000000005</v>
       </c>
       <c r="J27" s="0">
-        <v>1493</v>
+        <v>3395</v>
       </c>
       <c r="K27" s="0">
-        <v>4964.8400000000001</v>
+        <v>5578.6599999999999</v>
       </c>
       <c r="L27" s="0">
-        <v>27.739999999999998</v>
+        <v>17.539999999999999</v>
       </c>
       <c r="M27" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.035999999999999997</v>
       </c>
     </row>
     <row r="28">
@@ -1347,40 +1314,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>47935061897</v>
+        <v>71307801505</v>
       </c>
       <c r="C28" s="0">
-        <v>54231008623</v>
+        <v>85462342476</v>
       </c>
       <c r="D28" s="0">
-        <v>820936</v>
+        <v>1783066</v>
       </c>
       <c r="E28" s="0">
-        <v>182</v>
+        <v>293</v>
       </c>
       <c r="F28" s="0">
-        <v>184259</v>
+        <v>72294</v>
       </c>
       <c r="G28" s="0">
-        <v>2.79</v>
+        <v>1.51</v>
       </c>
       <c r="H28" s="0">
-        <v>10.98</v>
+        <v>12.699999999999999</v>
       </c>
       <c r="I28" s="0">
-        <v>88.390000000000001</v>
+        <v>83.439999999999998</v>
       </c>
       <c r="J28" s="0">
-        <v>1645</v>
+        <v>4141</v>
       </c>
       <c r="K28" s="0">
-        <v>4931.1099999999997</v>
+        <v>9419.4699999999993</v>
       </c>
       <c r="L28" s="0">
-        <v>27.489999999999998</v>
+        <v>32.920000000000002</v>
       </c>
       <c r="M28" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="29">
@@ -1388,40 +1355,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>11893993789</v>
+        <v>24695859448</v>
       </c>
       <c r="C29" s="0">
-        <v>13508447609</v>
+        <v>29615257922</v>
       </c>
       <c r="D29" s="0">
-        <v>1006591</v>
+        <v>2292203</v>
       </c>
       <c r="E29" s="0">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="F29" s="0">
-        <v>35352</v>
+        <v>16559</v>
       </c>
       <c r="G29" s="0">
-        <v>2.6299999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="H29" s="0">
-        <v>10.24</v>
+        <v>13.880000000000001</v>
       </c>
       <c r="I29" s="0">
-        <v>88.049999999999997</v>
+        <v>83.390000000000001</v>
       </c>
       <c r="J29" s="0">
-        <v>1633</v>
+        <v>5462</v>
       </c>
       <c r="K29" s="0">
-        <v>5409.0799999999999</v>
+        <v>10818.790000000001</v>
       </c>
       <c r="L29" s="0">
-        <v>23.120000000000001</v>
+        <v>33.07</v>
       </c>
       <c r="M29" s="0">
-        <v>0.055</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="30">
@@ -1429,491 +1396,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>38983770971</v>
+        <v>643056477120</v>
       </c>
       <c r="C30" s="0">
-        <v>46295620313</v>
+        <v>751898800983</v>
       </c>
       <c r="D30" s="0">
-        <v>0</v>
+        <v>822989</v>
       </c>
       <c r="E30" s="0">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="F30" s="0">
-        <v>62231</v>
+        <v>3058828</v>
       </c>
       <c r="G30" s="0">
-        <v>0</v>
+        <v>3.3500000000000001</v>
       </c>
       <c r="H30" s="0">
-        <v>0</v>
+        <v>10.77</v>
       </c>
       <c r="I30" s="0">
-        <v>84.209999999999994</v>
+        <v>85.519999999999996</v>
       </c>
       <c r="J30" s="0">
-        <v>3486</v>
+        <v>1286</v>
       </c>
       <c r="K30" s="0">
-        <v>6796.1999999999998</v>
+        <v>5245.5299999999997</v>
       </c>
       <c r="L30" s="0">
-        <v>31.859999999999999</v>
+        <v>28.350000000000001</v>
       </c>
       <c r="M30" s="0">
-        <v>0.068000000000000005</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>15381428931</v>
-      </c>
-      <c r="C31" s="0">
-        <v>17997226658</v>
-      </c>
-      <c r="D31" s="0">
-        <v>0</v>
-      </c>
-      <c r="E31" s="0">
-        <v>242</v>
-      </c>
-      <c r="F31" s="0">
-        <v>20000</v>
-      </c>
-      <c r="G31" s="0">
-        <v>0</v>
-      </c>
-      <c r="H31" s="0">
-        <v>0</v>
-      </c>
-      <c r="I31" s="0">
-        <v>85.469999999999999</v>
-      </c>
-      <c r="J31" s="0">
-        <v>3725</v>
-      </c>
-      <c r="K31" s="0">
-        <v>6753.1899999999996</v>
-      </c>
-      <c r="L31" s="0">
-        <v>27.960000000000001</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.058999999999999997</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>23791003183</v>
-      </c>
-      <c r="C32" s="0">
-        <v>28219020422</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1623649</v>
-      </c>
-      <c r="E32" s="0">
-        <v>260</v>
-      </c>
-      <c r="F32" s="0">
-        <v>31722</v>
-      </c>
-      <c r="G32" s="0">
-        <v>1.8300000000000001</v>
-      </c>
-      <c r="H32" s="0">
-        <v>13.41</v>
-      </c>
-      <c r="I32" s="0">
-        <v>84.310000000000002</v>
-      </c>
-      <c r="J32" s="0">
-        <v>3445</v>
-      </c>
-      <c r="K32" s="0">
-        <v>7730.7700000000004</v>
-      </c>
-      <c r="L32" s="0">
-        <v>29.920000000000002</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.064000000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>22893534970</v>
-      </c>
-      <c r="C33" s="0">
-        <v>26889504124</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1938681</v>
-      </c>
-      <c r="E33" s="0">
-        <v>291</v>
-      </c>
-      <c r="F33" s="0">
-        <v>22537</v>
-      </c>
-      <c r="G33" s="0">
-        <v>1.6200000000000001</v>
-      </c>
-      <c r="H33" s="0">
-        <v>13.869999999999999</v>
-      </c>
-      <c r="I33" s="0">
-        <v>85.140000000000001</v>
-      </c>
-      <c r="J33" s="0">
-        <v>4096</v>
-      </c>
-      <c r="K33" s="0">
-        <v>7631.8599999999997</v>
-      </c>
-      <c r="L33" s="0">
-        <v>26.199999999999999</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>847679219</v>
-      </c>
-      <c r="C34" s="0">
-        <v>1013162706</v>
-      </c>
-      <c r="D34" s="0">
-        <v>1608195</v>
-      </c>
-      <c r="E34" s="0">
-        <v>280</v>
-      </c>
-      <c r="F34" s="0">
-        <v>680</v>
-      </c>
-      <c r="G34" s="0">
-        <v>1.0800000000000001</v>
-      </c>
-      <c r="H34" s="0">
-        <v>11.789999999999999</v>
-      </c>
-      <c r="I34" s="0">
-        <v>83.670000000000002</v>
-      </c>
-      <c r="J34" s="0">
-        <v>5315</v>
-      </c>
-      <c r="K34" s="0">
-        <v>6881.9399999999996</v>
-      </c>
-      <c r="L34" s="0">
-        <v>24.550000000000001</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>9566236554</v>
-      </c>
-      <c r="C35" s="0">
-        <v>11200460405</v>
-      </c>
-      <c r="D35" s="0">
-        <v>2408701</v>
-      </c>
-      <c r="E35" s="0">
-        <v>305</v>
-      </c>
-      <c r="F35" s="0">
-        <v>5980</v>
-      </c>
-      <c r="G35" s="0">
-        <v>1.29</v>
-      </c>
-      <c r="H35" s="0">
-        <v>15.470000000000001</v>
-      </c>
-      <c r="I35" s="0">
-        <v>85.409999999999997</v>
-      </c>
-      <c r="J35" s="0">
-        <v>6139</v>
-      </c>
-      <c r="K35" s="0">
-        <v>7491.8299999999999</v>
-      </c>
-      <c r="L35" s="0">
-        <v>24.559999999999999</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.048000000000000001</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>13046758010</v>
-      </c>
-      <c r="C36" s="0">
-        <v>15577601393</v>
-      </c>
-      <c r="D36" s="0">
-        <v>1492107</v>
-      </c>
-      <c r="E36" s="0">
-        <v>228</v>
-      </c>
-      <c r="F36" s="0">
-        <v>17686</v>
-      </c>
-      <c r="G36" s="0">
-        <v>1.6899999999999999</v>
-      </c>
-      <c r="H36" s="0">
-        <v>13.380000000000001</v>
-      </c>
-      <c r="I36" s="0">
-        <v>83.75</v>
-      </c>
-      <c r="J36" s="0">
-        <v>3883</v>
-      </c>
-      <c r="K36" s="0">
-        <v>8280.1499999999996</v>
-      </c>
-      <c r="L36" s="0">
-        <v>36.479999999999997</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.073999999999999996</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>27220559776</v>
-      </c>
-      <c r="C37" s="0">
-        <v>32692611730</v>
-      </c>
-      <c r="D37" s="0">
-        <v>2094338</v>
-      </c>
-      <c r="E37" s="0">
-        <v>267</v>
-      </c>
-      <c r="F37" s="0">
-        <v>21800</v>
-      </c>
-      <c r="G37" s="0">
-        <v>1.3999999999999999</v>
-      </c>
-      <c r="H37" s="0">
-        <v>15.460000000000001</v>
-      </c>
-      <c r="I37" s="0">
-        <v>83.260000000000005</v>
-      </c>
-      <c r="J37" s="0">
-        <v>5651</v>
-      </c>
-      <c r="K37" s="0">
-        <v>8692.1399999999994</v>
-      </c>
-      <c r="L37" s="0">
-        <v>32.719999999999999</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.064000000000000001</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="0">
-        <v>4782436290</v>
-      </c>
-      <c r="C38" s="0">
-        <v>5372651340</v>
-      </c>
-      <c r="D38" s="0">
-        <v>0</v>
-      </c>
-      <c r="E38" s="0">
-        <v>318</v>
-      </c>
-      <c r="F38" s="0">
-        <v>4977</v>
-      </c>
-      <c r="G38" s="0">
-        <v>0</v>
-      </c>
-      <c r="H38" s="0">
-        <v>0</v>
-      </c>
-      <c r="I38" s="0">
-        <v>89.010000000000005</v>
-      </c>
-      <c r="J38" s="0">
-        <v>3395</v>
-      </c>
-      <c r="K38" s="0">
-        <v>5578.6599999999999</v>
-      </c>
-      <c r="L38" s="0">
-        <v>17.539999999999999</v>
-      </c>
-      <c r="M38" s="0">
-        <v>0.035999999999999997</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="0">
-        <v>71307801505</v>
-      </c>
-      <c r="C39" s="0">
-        <v>85462342476</v>
-      </c>
-      <c r="D39" s="0">
-        <v>1783066</v>
-      </c>
-      <c r="E39" s="0">
-        <v>293</v>
-      </c>
-      <c r="F39" s="0">
-        <v>72294</v>
-      </c>
-      <c r="G39" s="0">
-        <v>1.51</v>
-      </c>
-      <c r="H39" s="0">
-        <v>12.699999999999999</v>
-      </c>
-      <c r="I39" s="0">
-        <v>83.439999999999998</v>
-      </c>
-      <c r="J39" s="0">
-        <v>4141</v>
-      </c>
-      <c r="K39" s="0">
-        <v>9419.4699999999993</v>
-      </c>
-      <c r="L39" s="0">
-        <v>32.920000000000002</v>
-      </c>
-      <c r="M39" s="0">
-        <v>0.067000000000000004</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="0">
-        <v>24695859448</v>
-      </c>
-      <c r="C40" s="0">
-        <v>29615257922</v>
-      </c>
-      <c r="D40" s="0">
-        <v>0</v>
-      </c>
-      <c r="E40" s="0">
-        <v>325</v>
-      </c>
-      <c r="F40" s="0">
-        <v>16559</v>
-      </c>
-      <c r="G40" s="0">
-        <v>0</v>
-      </c>
-      <c r="H40" s="0">
-        <v>0</v>
-      </c>
-      <c r="I40" s="0">
-        <v>83.390000000000001</v>
-      </c>
-      <c r="J40" s="0">
-        <v>5462</v>
-      </c>
-      <c r="K40" s="0">
-        <v>10818.790000000001</v>
-      </c>
-      <c r="L40" s="0">
-        <v>33.07</v>
-      </c>
-      <c r="M40" s="0">
-        <v>0.066000000000000003</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="0">
-        <v>1046062680824</v>
-      </c>
-      <c r="C41" s="0">
-        <v>1235537403983</v>
-      </c>
-      <c r="D41" s="0">
-        <v>0</v>
-      </c>
-      <c r="E41" s="0">
-        <v>131</v>
-      </c>
-      <c r="F41" s="0">
-        <v>8398644</v>
-      </c>
-      <c r="G41" s="0">
-        <v>0</v>
-      </c>
-      <c r="H41" s="0">
-        <v>0</v>
-      </c>
-      <c r="I41" s="0">
-        <v>84.659999999999997</v>
-      </c>
-      <c r="J41" s="0">
-        <v>911</v>
-      </c>
-      <c r="K41" s="0">
-        <v>3935.23</v>
-      </c>
-      <c r="L41" s="0">
-        <v>25.949999999999999</v>
-      </c>
-      <c r="M41" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
   </sheetData>
